--- a/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_retail_building_supply.xlsx
+++ b/research/traditional_assets/database/data/saudi_arabia/saudi_arabia_retail_building_supply.xlsx
@@ -1400,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1537,22 +1537,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0946920329456668</v>
+        <v>0.09453864887977548</v>
       </c>
       <c r="C2">
-        <v>810.6968370566655</v>
+        <v>804.9692725692242</v>
       </c>
       <c r="D2">
-        <v>803.1068370566654</v>
+        <v>805.6342725692242</v>
       </c>
       <c r="E2">
-        <v>-77.8</v>
+        <v>-69.545</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>8.255000000000001</v>
       </c>
       <c r="G2">
         <v>7.59</v>
@@ -1573,28 +1573,28 @@
         <v>19.56</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4152265</v>
       </c>
       <c r="N2">
-        <v>19.56</v>
+        <v>19.1447735</v>
       </c>
       <c r="O2">
-        <v>3.911999999999999</v>
+        <v>3.828954699999999</v>
       </c>
       <c r="P2">
-        <v>15.648</v>
+        <v>15.3158188</v>
       </c>
       <c r="Q2">
-        <v>24.08799999999999</v>
+        <v>23.7558188</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0946920329456668</v>
+        <v>0.09508712008058129</v>
       </c>
       <c r="T2">
-        <v>0.9529967248041119</v>
+        <v>0.9606977084388927</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1611,7 +1611,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>47.10682001269186</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1619,22 +1619,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09453864887977548</v>
+        <v>0.09438526481388412</v>
       </c>
       <c r="C3">
-        <v>804.9692725692242</v>
+        <v>799.2576663496524</v>
       </c>
       <c r="D3">
-        <v>805.6342725692242</v>
+        <v>808.1776663496523</v>
       </c>
       <c r="E3">
-        <v>-69.545</v>
+        <v>-61.28999999999999</v>
       </c>
       <c r="F3">
-        <v>8.255000000000001</v>
+        <v>16.51</v>
       </c>
       <c r="G3">
         <v>7.59</v>
@@ -1655,28 +1655,28 @@
         <v>19.56</v>
       </c>
       <c r="M3">
-        <v>0.4152265</v>
+        <v>0.830453</v>
       </c>
       <c r="N3">
-        <v>19.1447735</v>
+        <v>18.729547</v>
       </c>
       <c r="O3">
-        <v>3.828954699999999</v>
+        <v>3.7459094</v>
       </c>
       <c r="P3">
-        <v>15.3158188</v>
+        <v>14.9836376</v>
       </c>
       <c r="Q3">
-        <v>23.7558188</v>
+        <v>23.4236376</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09508712008058129</v>
+        <v>0.09549027021824912</v>
       </c>
       <c r="T3">
-        <v>0.9606977084388927</v>
+        <v>0.9685558550049953</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1693,7 +1693,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>47.10682001269186</v>
+        <v>23.55341000634593</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1701,22 +1701,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09438526481388412</v>
+        <v>0.09423188074799281</v>
       </c>
       <c r="C4">
-        <v>799.2576663496524</v>
+        <v>793.5621700177481</v>
       </c>
       <c r="D4">
-        <v>808.1776663496523</v>
+        <v>810.7371700177481</v>
       </c>
       <c r="E4">
-        <v>-61.28999999999999</v>
+        <v>-53.035</v>
       </c>
       <c r="F4">
-        <v>16.51</v>
+        <v>24.765</v>
       </c>
       <c r="G4">
         <v>7.59</v>
@@ -1737,28 +1737,28 @@
         <v>19.56</v>
       </c>
       <c r="M4">
-        <v>0.830453</v>
+        <v>1.2456795</v>
       </c>
       <c r="N4">
-        <v>18.729547</v>
+        <v>18.31432049999999</v>
       </c>
       <c r="O4">
-        <v>3.7459094</v>
+        <v>3.662864099999999</v>
       </c>
       <c r="P4">
-        <v>14.9836376</v>
+        <v>14.6514564</v>
       </c>
       <c r="Q4">
-        <v>23.4236376</v>
+        <v>23.09145639999999</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09549027021824912</v>
+        <v>0.09590173272988949</v>
       </c>
       <c r="T4">
-        <v>0.9685558550049953</v>
+        <v>0.9765760252116362</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1775,7 +1775,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>23.55341000634593</v>
+        <v>15.70227333756395</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1783,22 +1783,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09423188074799281</v>
+        <v>0.09412649668210146</v>
       </c>
       <c r="C5">
-        <v>793.5621700177481</v>
+        <v>787.07511897353</v>
       </c>
       <c r="D5">
-        <v>810.7371700177481</v>
+        <v>812.50511897353</v>
       </c>
       <c r="E5">
-        <v>-53.035</v>
+        <v>-44.77999999999999</v>
       </c>
       <c r="F5">
-        <v>24.765</v>
+        <v>33.02</v>
       </c>
       <c r="G5">
         <v>7.59</v>
@@ -1819,45 +1819,45 @@
         <v>19.56</v>
       </c>
       <c r="M5">
-        <v>1.2456795</v>
+        <v>1.710436</v>
       </c>
       <c r="N5">
-        <v>18.31432049999999</v>
+        <v>17.84956399999999</v>
       </c>
       <c r="O5">
-        <v>3.662864099999999</v>
+        <v>3.569912799999999</v>
       </c>
       <c r="P5">
-        <v>14.6514564</v>
+        <v>14.27965119999999</v>
       </c>
       <c r="Q5">
-        <v>23.09145639999999</v>
+        <v>22.71965119999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09590173272988949</v>
+        <v>0.09632176737718903</v>
       </c>
       <c r="T5">
-        <v>0.9765760252116362</v>
+        <v>0.9847632822975824</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y5">
-        <v>15.70227333756395</v>
+        <v>11.4356807270193</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1865,22 +1865,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09412649668210146</v>
+        <v>0.09405311261621013</v>
       </c>
       <c r="C6">
-        <v>787.07511897353</v>
+        <v>780.0557890879542</v>
       </c>
       <c r="D6">
-        <v>812.50511897353</v>
+        <v>813.7407890879541</v>
       </c>
       <c r="E6">
-        <v>-44.77999999999999</v>
+        <v>-36.52499999999999</v>
       </c>
       <c r="F6">
-        <v>33.02</v>
+        <v>41.27500000000001</v>
       </c>
       <c r="G6">
         <v>7.59</v>
@@ -1901,45 +1901,45 @@
         <v>19.56</v>
       </c>
       <c r="M6">
-        <v>1.710436</v>
+        <v>2.2082125</v>
       </c>
       <c r="N6">
-        <v>17.84956399999999</v>
+        <v>17.35178749999999</v>
       </c>
       <c r="O6">
-        <v>3.569912799999999</v>
+        <v>3.470357499999999</v>
       </c>
       <c r="P6">
-        <v>14.27965119999999</v>
+        <v>13.88142999999999</v>
       </c>
       <c r="Q6">
-        <v>22.71965119999999</v>
+        <v>22.32142999999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09632176737718903</v>
+        <v>0.09675064485916857</v>
       </c>
       <c r="T6">
-        <v>0.9847632822975824</v>
+        <v>0.9931229026906008</v>
       </c>
       <c r="U6">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V6">
         <v>0.2</v>
       </c>
       <c r="W6">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>11.4356807270193</v>
+        <v>8.857843165003365</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1947,22 +1947,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09405311261621013</v>
+        <v>0.0939637285503188</v>
       </c>
       <c r="C7">
-        <v>780.0557890879542</v>
+        <v>773.3109599675677</v>
       </c>
       <c r="D7">
-        <v>813.7407890879541</v>
+        <v>815.2509599675676</v>
       </c>
       <c r="E7">
-        <v>-36.52499999999999</v>
+        <v>-28.27</v>
       </c>
       <c r="F7">
-        <v>41.27500000000001</v>
+        <v>49.53</v>
       </c>
       <c r="G7">
         <v>7.59</v>
@@ -1983,45 +1983,45 @@
         <v>19.56</v>
       </c>
       <c r="M7">
-        <v>2.2082125</v>
+        <v>2.689479</v>
       </c>
       <c r="N7">
-        <v>17.35178749999999</v>
+        <v>16.870521</v>
       </c>
       <c r="O7">
-        <v>3.470357499999999</v>
+        <v>3.3741042</v>
       </c>
       <c r="P7">
-        <v>13.88142999999999</v>
+        <v>13.4964168</v>
       </c>
       <c r="Q7">
-        <v>22.32142999999999</v>
+        <v>21.9364168</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09675064485916857</v>
+        <v>0.09718864739395618</v>
       </c>
       <c r="T7">
-        <v>0.9931229026906008</v>
+        <v>1.001660387347301</v>
       </c>
       <c r="U7">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y7">
-        <v>8.857843165003365</v>
+        <v>7.272784059663599</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.0939637285503188</v>
+        <v>0.09384234448442748</v>
       </c>
       <c r="C8">
-        <v>773.3109599675677</v>
+        <v>767.1157777659007</v>
       </c>
       <c r="D8">
-        <v>815.2509599675676</v>
+        <v>817.3107777659006</v>
       </c>
       <c r="E8">
-        <v>-28.27</v>
+        <v>-20.015</v>
       </c>
       <c r="F8">
-        <v>49.53</v>
+        <v>57.785</v>
       </c>
       <c r="G8">
         <v>7.59</v>
@@ -2065,28 +2065,28 @@
         <v>19.56</v>
       </c>
       <c r="M8">
-        <v>2.689479</v>
+        <v>3.1377255</v>
       </c>
       <c r="N8">
-        <v>16.870521</v>
+        <v>16.4222745</v>
       </c>
       <c r="O8">
-        <v>3.3741042</v>
+        <v>3.2844549</v>
       </c>
       <c r="P8">
-        <v>13.4964168</v>
+        <v>13.1378196</v>
       </c>
       <c r="Q8">
-        <v>21.9364168</v>
+        <v>21.5778196</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09718864739395618</v>
+        <v>0.09763606933809406</v>
       </c>
       <c r="T8">
-        <v>1.001660387347301</v>
+        <v>1.010381473824575</v>
       </c>
       <c r="U8">
         <v>0.0543</v>
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>7.272784059663599</v>
+        <v>6.233814908283086</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2111,22 +2111,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09384234448442746</v>
+        <v>0.09378496041853614</v>
       </c>
       <c r="C9">
-        <v>767.1157777659009</v>
+        <v>759.8381801669018</v>
       </c>
       <c r="D9">
-        <v>817.3107777659009</v>
+        <v>818.2881801669017</v>
       </c>
       <c r="E9">
-        <v>-20.01499999999999</v>
+        <v>-11.75999999999999</v>
       </c>
       <c r="F9">
-        <v>57.785</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="G9">
         <v>7.59</v>
@@ -2147,45 +2147,45 @@
         <v>19.56</v>
       </c>
       <c r="M9">
-        <v>3.1377255</v>
+        <v>3.652012</v>
       </c>
       <c r="N9">
-        <v>16.42227449999999</v>
+        <v>15.90798799999999</v>
       </c>
       <c r="O9">
-        <v>3.284454899999999</v>
+        <v>3.181597599999999</v>
       </c>
       <c r="P9">
-        <v>13.13781959999999</v>
+        <v>12.7263904</v>
       </c>
       <c r="Q9">
-        <v>21.57781959999999</v>
+        <v>21.1663904</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09763606933809406</v>
+        <v>0.09809321784623493</v>
       </c>
       <c r="T9">
-        <v>1.010381473824575</v>
+        <v>1.019292149138311</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.233814908283083</v>
+        <v>5.355951732907775</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2193,22 +2193,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09378496041853614</v>
+        <v>0.09367157635264479</v>
       </c>
       <c r="C10">
-        <v>759.8381801669018</v>
+        <v>753.5212997778935</v>
       </c>
       <c r="D10">
-        <v>818.2881801669017</v>
+        <v>820.2262997778935</v>
       </c>
       <c r="E10">
-        <v>-11.75999999999999</v>
+        <v>-3.504999999999995</v>
       </c>
       <c r="F10">
-        <v>66.04000000000001</v>
+        <v>74.295</v>
       </c>
       <c r="G10">
         <v>7.59</v>
@@ -2229,28 +2229,28 @@
         <v>19.56</v>
       </c>
       <c r="M10">
-        <v>3.652012</v>
+        <v>4.1085135</v>
       </c>
       <c r="N10">
-        <v>15.90798799999999</v>
+        <v>15.45148649999999</v>
       </c>
       <c r="O10">
-        <v>3.181597599999999</v>
+        <v>3.090297299999999</v>
       </c>
       <c r="P10">
-        <v>12.7263904</v>
+        <v>12.36118919999999</v>
       </c>
       <c r="Q10">
-        <v>21.1663904</v>
+        <v>20.8011892</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09809321784623493</v>
+        <v>0.09856041357433494</v>
       </c>
       <c r="T10">
-        <v>1.019292149138311</v>
+        <v>1.028398663469932</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2267,7 +2267,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.355951732907775</v>
+        <v>4.760845984806912</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2275,22 +2275,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09367157635264479</v>
+        <v>0.09375819228675346</v>
       </c>
       <c r="C11">
-        <v>753.5212997778935</v>
+        <v>743.7849122662259</v>
       </c>
       <c r="D11">
-        <v>820.2262997778935</v>
+        <v>818.7449122662258</v>
       </c>
       <c r="E11">
-        <v>-3.504999999999995</v>
+        <v>4.75</v>
       </c>
       <c r="F11">
-        <v>74.295</v>
+        <v>82.55</v>
       </c>
       <c r="G11">
         <v>7.59</v>
@@ -2311,45 +2311,45 @@
         <v>19.56</v>
       </c>
       <c r="M11">
-        <v>4.1085135</v>
+        <v>4.77139</v>
       </c>
       <c r="N11">
-        <v>15.45148649999999</v>
+        <v>14.78860999999999</v>
       </c>
       <c r="O11">
-        <v>3.090297299999999</v>
+        <v>2.957721999999999</v>
       </c>
       <c r="P11">
-        <v>12.36118919999999</v>
+        <v>11.830888</v>
       </c>
       <c r="Q11">
-        <v>20.8011892</v>
+        <v>20.270888</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09856041357433494</v>
+        <v>0.09903799142972607</v>
       </c>
       <c r="T11">
-        <v>1.028398663469932</v>
+        <v>1.037707544786699</v>
       </c>
       <c r="U11">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V11">
         <v>0.2</v>
       </c>
       <c r="W11">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y11">
-        <v>4.760845984806912</v>
+        <v>4.099434336744637</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2357,22 +2357,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09375819228675347</v>
+        <v>0.09397280822086211</v>
       </c>
       <c r="C12">
-        <v>743.7849122662255</v>
+        <v>731.8823004571509</v>
       </c>
       <c r="D12">
-        <v>818.7449122662256</v>
+        <v>815.0973004571508</v>
       </c>
       <c r="E12">
-        <v>4.750000000000014</v>
+        <v>13.00500000000001</v>
       </c>
       <c r="F12">
-        <v>82.55000000000001</v>
+        <v>90.80500000000001</v>
       </c>
       <c r="G12">
         <v>7.59</v>
@@ -2393,45 +2393,45 @@
         <v>19.56</v>
       </c>
       <c r="M12">
-        <v>4.771390000000001</v>
+        <v>5.566346500000001</v>
       </c>
       <c r="N12">
-        <v>14.78860999999999</v>
+        <v>13.99365349999999</v>
       </c>
       <c r="O12">
-        <v>2.957721999999999</v>
+        <v>2.798730699999999</v>
       </c>
       <c r="P12">
-        <v>11.830888</v>
+        <v>11.1949228</v>
       </c>
       <c r="Q12">
-        <v>20.270888</v>
+        <v>19.63492279999999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09903799142972608</v>
+        <v>0.09952630137175519</v>
       </c>
       <c r="T12">
-        <v>1.0377075447867</v>
+        <v>1.047225614447664</v>
       </c>
       <c r="U12">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V12">
         <v>0.2</v>
       </c>
       <c r="W12">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.099434336744636</v>
+        <v>3.513974561231499</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2439,22 +2439,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09397280822086211</v>
+        <v>0.0941762241549708</v>
       </c>
       <c r="C13">
-        <v>731.8823004571509</v>
+        <v>720.1999188940338</v>
       </c>
       <c r="D13">
-        <v>815.0973004571508</v>
+        <v>811.6699188940338</v>
       </c>
       <c r="E13">
-        <v>13.00500000000001</v>
+        <v>21.26000000000001</v>
       </c>
       <c r="F13">
-        <v>90.80500000000001</v>
+        <v>99.06</v>
       </c>
       <c r="G13">
         <v>7.59</v>
@@ -2475,45 +2475,45 @@
         <v>19.56</v>
       </c>
       <c r="M13">
-        <v>5.566346500000001</v>
+        <v>6.349746000000001</v>
       </c>
       <c r="N13">
-        <v>13.99365349999999</v>
+        <v>13.210254</v>
       </c>
       <c r="O13">
-        <v>2.798730699999999</v>
+        <v>2.642050799999999</v>
       </c>
       <c r="P13">
-        <v>11.1949228</v>
+        <v>10.5682032</v>
       </c>
       <c r="Q13">
-        <v>19.63492279999999</v>
+        <v>19.0082032</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09952630137175519</v>
+        <v>0.1000257092670123</v>
       </c>
       <c r="T13">
-        <v>1.047225614447664</v>
+        <v>1.056960003873652</v>
       </c>
       <c r="U13">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V13">
         <v>0.2</v>
       </c>
       <c r="W13">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>3.513974561231499</v>
+        <v>3.080438178157046</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2521,22 +2521,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0941762241549708</v>
+        <v>0.09494444008907947</v>
       </c>
       <c r="C14">
-        <v>720.1999188940338</v>
+        <v>699.2570591117092</v>
       </c>
       <c r="D14">
-        <v>811.6699188940338</v>
+        <v>798.9820591117092</v>
       </c>
       <c r="E14">
-        <v>21.26000000000001</v>
+        <v>29.515</v>
       </c>
       <c r="F14">
-        <v>99.06</v>
+        <v>107.315</v>
       </c>
       <c r="G14">
         <v>7.59</v>
@@ -2557,45 +2557,45 @@
         <v>19.56</v>
       </c>
       <c r="M14">
-        <v>6.349746000000001</v>
+        <v>7.715948500000001</v>
       </c>
       <c r="N14">
-        <v>13.210254</v>
+        <v>11.8440515</v>
       </c>
       <c r="O14">
-        <v>2.642050799999999</v>
+        <v>2.368810299999999</v>
       </c>
       <c r="P14">
-        <v>10.5682032</v>
+        <v>9.475241199999996</v>
       </c>
       <c r="Q14">
-        <v>19.0082032</v>
+        <v>17.9152412</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1000257092670123</v>
+        <v>0.1005365978035396</v>
       </c>
       <c r="T14">
-        <v>1.056960003873652</v>
+        <v>1.066918172366902</v>
       </c>
       <c r="U14">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V14">
         <v>0.2</v>
       </c>
       <c r="W14">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.080438178157046</v>
+        <v>2.535009143723548</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2603,22 +2603,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09494444008907947</v>
+        <v>0.09540065602318813</v>
       </c>
       <c r="C15">
-        <v>699.2570591117092</v>
+        <v>683.6531977123095</v>
       </c>
       <c r="D15">
-        <v>798.9820591117092</v>
+        <v>791.6331977123095</v>
       </c>
       <c r="E15">
-        <v>29.515</v>
+        <v>37.77000000000001</v>
       </c>
       <c r="F15">
-        <v>107.315</v>
+        <v>115.57</v>
       </c>
       <c r="G15">
         <v>7.59</v>
@@ -2639,45 +2639,45 @@
         <v>19.56</v>
       </c>
       <c r="M15">
-        <v>7.715948500000001</v>
+        <v>8.760206000000002</v>
       </c>
       <c r="N15">
-        <v>11.8440515</v>
+        <v>10.79979399999999</v>
       </c>
       <c r="O15">
-        <v>2.368810299999999</v>
+        <v>2.159958799999999</v>
       </c>
       <c r="P15">
-        <v>9.475241199999996</v>
+        <v>8.639835199999995</v>
       </c>
       <c r="Q15">
-        <v>17.9152412</v>
+        <v>17.07983519999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1005365978035396</v>
+        <v>0.1010593674688234</v>
       </c>
       <c r="T15">
-        <v>1.066918172366902</v>
+        <v>1.07710792617395</v>
       </c>
       <c r="U15">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V15">
         <v>0.2</v>
       </c>
       <c r="W15">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y15">
-        <v>2.535009143723548</v>
+        <v>2.232824205275537</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2685,22 +2685,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09540065602318813</v>
+        <v>0.09545127195729682</v>
       </c>
       <c r="C16">
-        <v>683.6531977123095</v>
+        <v>674.5911840710856</v>
       </c>
       <c r="D16">
-        <v>791.6331977123095</v>
+        <v>790.8261840710857</v>
       </c>
       <c r="E16">
-        <v>37.77000000000001</v>
+        <v>46.02500000000002</v>
       </c>
       <c r="F16">
-        <v>115.57</v>
+        <v>123.825</v>
       </c>
       <c r="G16">
         <v>7.59</v>
@@ -2721,28 +2721,28 @@
         <v>19.56</v>
       </c>
       <c r="M16">
-        <v>8.760206000000002</v>
+        <v>9.385935000000002</v>
       </c>
       <c r="N16">
-        <v>10.79979399999999</v>
+        <v>10.17406499999999</v>
       </c>
       <c r="O16">
-        <v>2.159958799999999</v>
+        <v>2.034812999999999</v>
       </c>
       <c r="P16">
-        <v>8.639835199999995</v>
+        <v>8.139251999999995</v>
       </c>
       <c r="Q16">
-        <v>17.07983519999999</v>
+        <v>16.579252</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1010593674688234</v>
+        <v>0.1015944375968198</v>
       </c>
       <c r="T16">
-        <v>1.07710792617395</v>
+        <v>1.087537438894104</v>
       </c>
       <c r="U16">
         <v>0.07580000000000001</v>
@@ -2759,7 +2759,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>2.232824205275537</v>
+        <v>2.083969258257168</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2767,22 +2767,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0954512719572968</v>
+        <v>0.09731948789140546</v>
       </c>
       <c r="C17">
-        <v>674.591184071086</v>
+        <v>637.6589953283303</v>
       </c>
       <c r="D17">
-        <v>790.826184071086</v>
+        <v>762.1489953283303</v>
       </c>
       <c r="E17">
-        <v>46.02499999999999</v>
+        <v>54.28000000000002</v>
       </c>
       <c r="F17">
-        <v>123.825</v>
+        <v>132.08</v>
       </c>
       <c r="G17">
         <v>7.59</v>
@@ -2803,45 +2803,45 @@
         <v>19.56</v>
       </c>
       <c r="M17">
-        <v>9.385935</v>
+        <v>11.8872</v>
       </c>
       <c r="N17">
-        <v>10.174065</v>
+        <v>7.672799999999995</v>
       </c>
       <c r="O17">
-        <v>2.034812999999999</v>
+        <v>1.534559999999999</v>
       </c>
       <c r="P17">
-        <v>8.139251999999995</v>
+        <v>6.138239999999996</v>
       </c>
       <c r="Q17">
-        <v>16.579252</v>
+        <v>14.57824</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1015944375968198</v>
+        <v>0.1021422474897684</v>
       </c>
       <c r="T17">
-        <v>1.087537438894104</v>
+        <v>1.098215273345691</v>
       </c>
       <c r="U17">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y17">
-        <v>2.083969258257168</v>
+        <v>1.645467393498889</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2849,22 +2849,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09731948789140546</v>
+        <v>0.09748370382551412</v>
       </c>
       <c r="C18">
-        <v>637.6589953283303</v>
+        <v>626.982400126478</v>
       </c>
       <c r="D18">
-        <v>762.1489953283303</v>
+        <v>759.727400126478</v>
       </c>
       <c r="E18">
-        <v>54.28000000000002</v>
+        <v>62.53500000000001</v>
       </c>
       <c r="F18">
-        <v>132.08</v>
+        <v>140.335</v>
       </c>
       <c r="G18">
         <v>7.59</v>
@@ -2885,28 +2885,28 @@
         <v>19.56</v>
       </c>
       <c r="M18">
-        <v>11.8872</v>
+        <v>12.63015</v>
       </c>
       <c r="N18">
-        <v>7.672799999999995</v>
+        <v>6.929849999999995</v>
       </c>
       <c r="O18">
-        <v>1.534559999999999</v>
+        <v>1.385969999999999</v>
       </c>
       <c r="P18">
-        <v>6.138239999999996</v>
+        <v>5.543879999999996</v>
       </c>
       <c r="Q18">
-        <v>14.57824</v>
+        <v>13.98388</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1021422474897684</v>
+        <v>0.1027032576211014</v>
       </c>
       <c r="T18">
-        <v>1.098215273345691</v>
+        <v>1.109150405012978</v>
       </c>
       <c r="U18">
         <v>0.09</v>
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>1.645467393498889</v>
+        <v>1.548675193881307</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2931,22 +2931,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09748370382551412</v>
+        <v>0.1065547713992549</v>
       </c>
       <c r="C19">
-        <v>626.982400126478</v>
+        <v>505.2953449076145</v>
       </c>
       <c r="D19">
-        <v>759.727400126478</v>
+        <v>646.2953449076145</v>
       </c>
       <c r="E19">
-        <v>62.53500000000001</v>
+        <v>70.79000000000001</v>
       </c>
       <c r="F19">
-        <v>140.335</v>
+        <v>148.59</v>
       </c>
       <c r="G19">
         <v>7.59</v>
@@ -2967,45 +2967,45 @@
         <v>19.56</v>
       </c>
       <c r="M19">
-        <v>12.63015</v>
+        <v>21.813012</v>
       </c>
       <c r="N19">
-        <v>6.929849999999995</v>
+        <v>-2.253012000000009</v>
       </c>
       <c r="O19">
-        <v>1.385969999999999</v>
+        <v>-0.4506024000000018</v>
       </c>
       <c r="P19">
-        <v>5.543879999999996</v>
+        <v>-1.802409600000007</v>
       </c>
       <c r="Q19">
-        <v>13.98388</v>
+        <v>6.637590399999993</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1027032576211014</v>
+        <v>0.1034996554786972</v>
       </c>
       <c r="T19">
-        <v>1.109150405012978</v>
+        <v>1.124673681592075</v>
       </c>
       <c r="U19">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V19">
-        <v>0.2</v>
+        <v>0.1793424952042386</v>
       </c>
       <c r="W19">
-        <v>0.07199999999999999</v>
+        <v>0.1204725217040178</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y19">
-        <v>1.548675193881307</v>
+        <v>0.8967124760211929</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3013,22 +3013,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.106554771399255</v>
+        <v>0.107564771399255</v>
       </c>
       <c r="C20">
-        <v>505.2953449076144</v>
+        <v>486.4718884304232</v>
       </c>
       <c r="D20">
-        <v>646.2953449076144</v>
+        <v>635.7268884304232</v>
       </c>
       <c r="E20">
-        <v>70.79000000000001</v>
+        <v>79.045</v>
       </c>
       <c r="F20">
-        <v>148.59</v>
+        <v>156.845</v>
       </c>
       <c r="G20">
         <v>7.59</v>
@@ -3049,37 +3049,37 @@
         <v>19.56</v>
       </c>
       <c r="M20">
-        <v>21.813012</v>
+        <v>23.024846</v>
       </c>
       <c r="N20">
-        <v>-2.253012000000009</v>
+        <v>-3.464846000000009</v>
       </c>
       <c r="O20">
-        <v>-0.4506024000000018</v>
+        <v>-0.6929692000000017</v>
       </c>
       <c r="P20">
-        <v>-1.802409600000007</v>
+        <v>-2.771876800000007</v>
       </c>
       <c r="Q20">
-        <v>6.637590399999993</v>
+        <v>5.668123199999993</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1034996554786972</v>
+        <v>0.1042119969043602</v>
       </c>
       <c r="T20">
-        <v>1.124673681592075</v>
+        <v>1.138558541858644</v>
       </c>
       <c r="U20">
         <v>0.1468</v>
       </c>
       <c r="V20">
-        <v>0.1793424952042386</v>
+        <v>0.1699034165092786</v>
       </c>
       <c r="W20">
-        <v>0.1204725217040178</v>
+        <v>0.1218581784564379</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.8967124760211929</v>
+        <v>0.8495170825463932</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.107564771399255</v>
+        <v>0.1085747713992549</v>
       </c>
       <c r="C21">
-        <v>486.4718884304232</v>
+        <v>467.9885093698133</v>
       </c>
       <c r="D21">
-        <v>635.7268884304232</v>
+        <v>625.4985093698133</v>
       </c>
       <c r="E21">
-        <v>79.045</v>
+        <v>87.30000000000003</v>
       </c>
       <c r="F21">
-        <v>156.845</v>
+        <v>165.1</v>
       </c>
       <c r="G21">
         <v>7.59</v>
@@ -3131,37 +3131,37 @@
         <v>19.56</v>
       </c>
       <c r="M21">
-        <v>23.024846</v>
+        <v>24.23668000000001</v>
       </c>
       <c r="N21">
-        <v>-3.464846000000009</v>
+        <v>-4.676680000000012</v>
       </c>
       <c r="O21">
-        <v>-0.6929692000000017</v>
+        <v>-0.9353360000000024</v>
       </c>
       <c r="P21">
-        <v>-2.771876800000007</v>
+        <v>-3.74134400000001</v>
       </c>
       <c r="Q21">
-        <v>5.668123199999993</v>
+        <v>4.69865599999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1042119969043602</v>
+        <v>0.1049421468656647</v>
       </c>
       <c r="T21">
-        <v>1.138558541858644</v>
+        <v>1.152790523631877</v>
       </c>
       <c r="U21">
         <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.1699034165092786</v>
+        <v>0.1614082456838147</v>
       </c>
       <c r="W21">
-        <v>0.1218581784564379</v>
+        <v>0.123105269533616</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.8495170825463932</v>
+        <v>0.8070412284190734</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3177,22 +3177,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1085747713992549</v>
+        <v>0.1213492187820702</v>
       </c>
       <c r="C22">
-        <v>467.9885093698133</v>
+        <v>353.9693740844015</v>
       </c>
       <c r="D22">
-        <v>625.4985093698133</v>
+        <v>519.7343740844015</v>
       </c>
       <c r="E22">
-        <v>87.30000000000003</v>
+        <v>95.55500000000002</v>
       </c>
       <c r="F22">
-        <v>165.1</v>
+        <v>173.355</v>
       </c>
       <c r="G22">
         <v>7.59</v>
@@ -3213,45 +3213,45 @@
         <v>19.56</v>
       </c>
       <c r="M22">
-        <v>24.23668000000001</v>
+        <v>34.809684</v>
       </c>
       <c r="N22">
-        <v>-4.676680000000012</v>
+        <v>-15.24968400000001</v>
       </c>
       <c r="O22">
-        <v>-0.9353360000000024</v>
+        <v>-3.049936800000002</v>
       </c>
       <c r="P22">
-        <v>-3.74134400000001</v>
+        <v>-12.19974720000001</v>
       </c>
       <c r="Q22">
-        <v>4.69865599999999</v>
+        <v>-3.759747200000009</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1049421468656647</v>
+        <v>0.1062280568042366</v>
       </c>
       <c r="T22">
-        <v>1.152790523631877</v>
+        <v>1.177855301797554</v>
       </c>
       <c r="U22">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.1614082456838147</v>
+        <v>0.1123825197608803</v>
       </c>
       <c r="W22">
-        <v>0.123105269533616</v>
+        <v>0.1782335900320152</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y22">
-        <v>0.8070412284190734</v>
+        <v>0.5619125988044015</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3259,22 +3259,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1213492187820702</v>
+        <v>0.1228992187820701</v>
       </c>
       <c r="C23">
-        <v>353.9693740844017</v>
+        <v>335.2656523910223</v>
       </c>
       <c r="D23">
-        <v>519.7343740844017</v>
+        <v>509.2856523910223</v>
       </c>
       <c r="E23">
-        <v>95.55499999999999</v>
+        <v>103.81</v>
       </c>
       <c r="F23">
-        <v>173.355</v>
+        <v>181.61</v>
       </c>
       <c r="G23">
         <v>7.59</v>
@@ -3295,37 +3295,37 @@
         <v>19.56</v>
       </c>
       <c r="M23">
-        <v>34.809684</v>
+        <v>36.467288</v>
       </c>
       <c r="N23">
-        <v>-15.249684</v>
+        <v>-16.90728800000001</v>
       </c>
       <c r="O23">
-        <v>-3.049936800000001</v>
+        <v>-3.381457600000002</v>
       </c>
       <c r="P23">
-        <v>-12.1997472</v>
+        <v>-13.52583040000001</v>
       </c>
       <c r="Q23">
-        <v>-3.759747200000001</v>
+        <v>-5.085830400000008</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1062280568042366</v>
+        <v>0.107002775481214</v>
       </c>
       <c r="T23">
-        <v>1.177855301797554</v>
+        <v>1.192956010794959</v>
       </c>
       <c r="U23">
         <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.1123825197608803</v>
+        <v>0.107274223408113</v>
       </c>
       <c r="W23">
-        <v>0.1782335900320152</v>
+        <v>0.1792593359396509</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.5619125988044016</v>
+        <v>0.5363711170405651</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3341,22 +3341,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1228992187820701</v>
+        <v>0.1244492187820701</v>
       </c>
       <c r="C24">
-        <v>335.2656523910223</v>
+        <v>316.9737725156681</v>
       </c>
       <c r="D24">
-        <v>509.2856523910223</v>
+        <v>499.2487725156682</v>
       </c>
       <c r="E24">
-        <v>103.81</v>
+        <v>112.065</v>
       </c>
       <c r="F24">
-        <v>181.61</v>
+        <v>189.865</v>
       </c>
       <c r="G24">
         <v>7.59</v>
@@ -3377,37 +3377,37 @@
         <v>19.56</v>
       </c>
       <c r="M24">
-        <v>36.467288</v>
+        <v>38.124892</v>
       </c>
       <c r="N24">
-        <v>-16.90728800000001</v>
+        <v>-18.56489200000001</v>
       </c>
       <c r="O24">
-        <v>-3.381457600000002</v>
+        <v>-3.712978400000002</v>
       </c>
       <c r="P24">
-        <v>-13.52583040000001</v>
+        <v>-14.85191360000001</v>
       </c>
       <c r="Q24">
-        <v>-5.085830400000008</v>
+        <v>-6.411913600000007</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.107002775481214</v>
+        <v>0.1077976167212298</v>
       </c>
       <c r="T24">
-        <v>1.192956010794959</v>
+        <v>1.208448946000088</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.107274223408113</v>
+        <v>0.1026101267381951</v>
       </c>
       <c r="W24">
-        <v>0.1792593359396509</v>
+        <v>0.1801958865509704</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.5363711170405651</v>
+        <v>0.5130506336909753</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3423,22 +3423,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1244492187820701</v>
+        <v>0.1345704884277919</v>
       </c>
       <c r="C25">
-        <v>316.9737725156681</v>
+        <v>251.7963477727091</v>
       </c>
       <c r="D25">
-        <v>499.2487725156682</v>
+        <v>442.3263477727091</v>
       </c>
       <c r="E25">
-        <v>112.065</v>
+        <v>120.32</v>
       </c>
       <c r="F25">
-        <v>189.865</v>
+        <v>198.12</v>
       </c>
       <c r="G25">
         <v>7.59</v>
@@ -3459,45 +3459,45 @@
         <v>19.56</v>
       </c>
       <c r="M25">
-        <v>38.124892</v>
+        <v>46.71669600000001</v>
       </c>
       <c r="N25">
-        <v>-18.56489200000001</v>
+        <v>-27.15669600000001</v>
       </c>
       <c r="O25">
-        <v>-3.712978400000002</v>
+        <v>-5.431339200000003</v>
       </c>
       <c r="P25">
-        <v>-14.85191360000001</v>
+        <v>-21.72535680000001</v>
       </c>
       <c r="Q25">
-        <v>-6.411913600000007</v>
+        <v>-13.28535680000001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1077976167212298</v>
+        <v>0.1088387296329852</v>
       </c>
       <c r="T25">
-        <v>1.208448946000088</v>
+        <v>1.228742174472644</v>
       </c>
       <c r="U25">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.1026101267381951</v>
+        <v>0.08373879865134295</v>
       </c>
       <c r="W25">
-        <v>0.1801958865509704</v>
+        <v>0.2160543912780133</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y25">
-        <v>0.5130506336909753</v>
+        <v>0.4186939932567147</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3505,22 +3505,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1345704884277919</v>
+        <v>0.1364704884277919</v>
       </c>
       <c r="C26">
-        <v>251.7963477727091</v>
+        <v>234.2723995698169</v>
       </c>
       <c r="D26">
-        <v>442.3263477727091</v>
+        <v>433.0573995698169</v>
       </c>
       <c r="E26">
-        <v>120.32</v>
+        <v>128.575</v>
       </c>
       <c r="F26">
-        <v>198.12</v>
+        <v>206.375</v>
       </c>
       <c r="G26">
         <v>7.59</v>
@@ -3541,37 +3541,37 @@
         <v>19.56</v>
       </c>
       <c r="M26">
-        <v>46.71669600000001</v>
+        <v>48.663225</v>
       </c>
       <c r="N26">
-        <v>-27.15669600000001</v>
+        <v>-29.10322500000001</v>
       </c>
       <c r="O26">
-        <v>-5.431339200000003</v>
+        <v>-5.820645000000003</v>
       </c>
       <c r="P26">
-        <v>-21.72535680000001</v>
+        <v>-23.28258000000001</v>
       </c>
       <c r="Q26">
-        <v>-13.28535680000001</v>
+        <v>-14.84258000000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1088387296329852</v>
+        <v>0.1096792460280916</v>
       </c>
       <c r="T26">
-        <v>1.228742174472644</v>
+        <v>1.245125403465612</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.08373879865134295</v>
+        <v>0.08038924670528924</v>
       </c>
       <c r="W26">
-        <v>0.2160543912780133</v>
+        <v>0.2168442156268928</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3579,7 +3579,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.4186939932567147</v>
+        <v>0.4019462335264462</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3587,22 +3587,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1364704884277919</v>
+        <v>0.1383704884277919</v>
       </c>
       <c r="C27">
-        <v>234.2723995698169</v>
+        <v>217.1289398332727</v>
       </c>
       <c r="D27">
-        <v>433.0573995698169</v>
+        <v>424.1689398332728</v>
       </c>
       <c r="E27">
-        <v>128.575</v>
+        <v>136.83</v>
       </c>
       <c r="F27">
-        <v>206.375</v>
+        <v>214.63</v>
       </c>
       <c r="G27">
         <v>7.59</v>
@@ -3623,37 +3623,37 @@
         <v>19.56</v>
       </c>
       <c r="M27">
-        <v>48.663225</v>
+        <v>50.609754</v>
       </c>
       <c r="N27">
-        <v>-29.10322500000001</v>
+        <v>-31.04975400000001</v>
       </c>
       <c r="O27">
-        <v>-5.820645000000003</v>
+        <v>-6.209950800000001</v>
       </c>
       <c r="P27">
-        <v>-23.28258000000001</v>
+        <v>-24.83980320000001</v>
       </c>
       <c r="Q27">
-        <v>-14.84258000000001</v>
+        <v>-16.39980320000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1096792460280916</v>
+        <v>0.1105424790825253</v>
       </c>
       <c r="T27">
-        <v>1.245125403465612</v>
+        <v>1.261951422431364</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.08038924670528924</v>
+        <v>0.07729735260123966</v>
       </c>
       <c r="W27">
-        <v>0.2168442156268928</v>
+        <v>0.2175732842566277</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.4019462335264462</v>
+        <v>0.3864867630061982</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3669,22 +3669,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1383704884277919</v>
+        <v>0.1402704884277919</v>
       </c>
       <c r="C28">
-        <v>217.1289398332727</v>
+        <v>200.343011295741</v>
       </c>
       <c r="D28">
-        <v>424.1689398332728</v>
+        <v>415.638011295741</v>
       </c>
       <c r="E28">
-        <v>136.83</v>
+        <v>145.085</v>
       </c>
       <c r="F28">
-        <v>214.63</v>
+        <v>222.885</v>
       </c>
       <c r="G28">
         <v>7.59</v>
@@ -3705,37 +3705,37 @@
         <v>19.56</v>
       </c>
       <c r="M28">
-        <v>50.609754</v>
+        <v>52.55628300000001</v>
       </c>
       <c r="N28">
-        <v>-31.04975400000001</v>
+        <v>-32.99628300000001</v>
       </c>
       <c r="O28">
-        <v>-6.209950800000001</v>
+        <v>-6.599256600000003</v>
       </c>
       <c r="P28">
-        <v>-24.83980320000001</v>
+        <v>-26.39702640000001</v>
       </c>
       <c r="Q28">
-        <v>-16.39980320000001</v>
+        <v>-17.95702640000001</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1105424790825253</v>
+        <v>0.1114293623576284</v>
       </c>
       <c r="T28">
-        <v>1.261951422431364</v>
+        <v>1.279238428218095</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.07729735260123966</v>
+        <v>0.07443448769008262</v>
       </c>
       <c r="W28">
-        <v>0.2175732842566277</v>
+        <v>0.2182483478026785</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3864867630061982</v>
+        <v>0.3721724384504131</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3751,22 +3751,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1402704884277919</v>
+        <v>0.1421704884277919</v>
       </c>
       <c r="C29">
-        <v>200.343011295741</v>
+        <v>183.8934671531778</v>
       </c>
       <c r="D29">
-        <v>415.638011295741</v>
+        <v>407.4434671531778</v>
       </c>
       <c r="E29">
-        <v>145.085</v>
+        <v>153.34</v>
       </c>
       <c r="F29">
-        <v>222.885</v>
+        <v>231.14</v>
       </c>
       <c r="G29">
         <v>7.59</v>
@@ -3787,37 +3787,37 @@
         <v>19.56</v>
       </c>
       <c r="M29">
-        <v>52.55628300000001</v>
+        <v>54.50281200000001</v>
       </c>
       <c r="N29">
-        <v>-32.99628300000001</v>
+        <v>-34.94281200000001</v>
       </c>
       <c r="O29">
-        <v>-6.599256600000003</v>
+        <v>-6.988562400000003</v>
       </c>
       <c r="P29">
-        <v>-26.39702640000001</v>
+        <v>-27.95424960000001</v>
       </c>
       <c r="Q29">
-        <v>-17.95702640000001</v>
+        <v>-19.51424960000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1114293623576284</v>
+        <v>0.1123408812792621</v>
       </c>
       <c r="T29">
-        <v>1.279238428218095</v>
+        <v>1.297005628610013</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.07443448769008262</v>
+        <v>0.07177611312972253</v>
       </c>
       <c r="W29">
-        <v>0.2182483478026785</v>
+        <v>0.2188751925240114</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3721724384504131</v>
+        <v>0.3588805656486126</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3833,22 +3833,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1421704884277919</v>
+        <v>0.144070488427792</v>
       </c>
       <c r="C30">
-        <v>183.8934671531778</v>
+        <v>167.7607960438102</v>
       </c>
       <c r="D30">
-        <v>407.4434671531778</v>
+        <v>399.5657960438103</v>
       </c>
       <c r="E30">
-        <v>153.34</v>
+        <v>161.595</v>
       </c>
       <c r="F30">
-        <v>231.14</v>
+        <v>239.395</v>
       </c>
       <c r="G30">
         <v>7.59</v>
@@ -3869,37 +3869,37 @@
         <v>19.56</v>
       </c>
       <c r="M30">
-        <v>54.50281200000001</v>
+        <v>56.44934100000001</v>
       </c>
       <c r="N30">
-        <v>-34.94281200000001</v>
+        <v>-36.88934100000002</v>
       </c>
       <c r="O30">
-        <v>-6.988562400000003</v>
+        <v>-7.377868200000004</v>
       </c>
       <c r="P30">
-        <v>-27.95424960000001</v>
+        <v>-29.51147280000001</v>
       </c>
       <c r="Q30">
-        <v>-19.51424960000001</v>
+        <v>-21.07147280000002</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1123408812792621</v>
+        <v>0.1132780767902377</v>
       </c>
       <c r="T30">
-        <v>1.297005628610013</v>
+        <v>1.315273313520013</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.07177611312972253</v>
+        <v>0.06930107474593898</v>
       </c>
       <c r="W30">
-        <v>0.2188751925240114</v>
+        <v>0.2194588065749076</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.3588805656486126</v>
+        <v>0.3465053737296949</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3915,22 +3915,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1440704884277919</v>
+        <v>0.1459704884277919</v>
       </c>
       <c r="C31">
-        <v>167.7607960438106</v>
+        <v>151.9269669455527</v>
       </c>
       <c r="D31">
-        <v>399.5657960438106</v>
+        <v>391.9869669455528</v>
       </c>
       <c r="E31">
-        <v>161.595</v>
+        <v>169.85</v>
       </c>
       <c r="F31">
-        <v>239.395</v>
+        <v>247.65</v>
       </c>
       <c r="G31">
         <v>7.59</v>
@@ -3951,37 +3951,37 @@
         <v>19.56</v>
       </c>
       <c r="M31">
-        <v>56.449341</v>
+        <v>58.39587</v>
       </c>
       <c r="N31">
-        <v>-36.889341</v>
+        <v>-38.83587</v>
       </c>
       <c r="O31">
-        <v>-7.377868200000001</v>
+        <v>-7.767174000000001</v>
       </c>
       <c r="P31">
-        <v>-29.5114728</v>
+        <v>-31.068696</v>
       </c>
       <c r="Q31">
-        <v>-21.0714728</v>
+        <v>-22.628696</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1132780767902376</v>
+        <v>0.1142420493158124</v>
       </c>
       <c r="T31">
-        <v>1.315273313520013</v>
+        <v>1.334062932284585</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.06930107474593901</v>
+        <v>0.06699103892107437</v>
       </c>
       <c r="W31">
-        <v>0.2194588065749076</v>
+        <v>0.2200035130224107</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.346505373729695</v>
+        <v>0.3349551946053718</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3997,22 +3997,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1459704884277919</v>
+        <v>0.1478704884277919</v>
       </c>
       <c r="C32">
-        <v>151.9269669455527</v>
+        <v>136.375291396445</v>
       </c>
       <c r="D32">
-        <v>391.9869669455528</v>
+        <v>384.690291396445</v>
       </c>
       <c r="E32">
-        <v>169.85</v>
+        <v>178.105</v>
       </c>
       <c r="F32">
-        <v>247.65</v>
+        <v>255.905</v>
       </c>
       <c r="G32">
         <v>7.59</v>
@@ -4033,37 +4033,37 @@
         <v>19.56</v>
       </c>
       <c r="M32">
-        <v>58.39587</v>
+        <v>60.342399</v>
       </c>
       <c r="N32">
-        <v>-38.83587</v>
+        <v>-40.78239900000001</v>
       </c>
       <c r="O32">
-        <v>-7.767174000000001</v>
+        <v>-8.156479800000001</v>
       </c>
       <c r="P32">
-        <v>-31.068696</v>
+        <v>-32.62591920000001</v>
       </c>
       <c r="Q32">
-        <v>-22.628696</v>
+        <v>-24.18591920000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1142420493158124</v>
+        <v>0.1152339630740127</v>
       </c>
       <c r="T32">
-        <v>1.334062932284585</v>
+        <v>1.353397177680014</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.06699103892107437</v>
+        <v>0.06483003766555584</v>
       </c>
       <c r="W32">
-        <v>0.2200035130224107</v>
+        <v>0.2205130771184619</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -4071,7 +4071,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3349551946053718</v>
+        <v>0.3241501883277792</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4079,22 +4079,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1478704884277919</v>
+        <v>0.1497704884277919</v>
       </c>
       <c r="C33">
-        <v>136.375291396445</v>
+        <v>121.0903008221402</v>
       </c>
       <c r="D33">
-        <v>384.690291396445</v>
+        <v>377.6603008221402</v>
       </c>
       <c r="E33">
-        <v>178.105</v>
+        <v>186.36</v>
       </c>
       <c r="F33">
-        <v>255.905</v>
+        <v>264.16</v>
       </c>
       <c r="G33">
         <v>7.59</v>
@@ -4115,37 +4115,37 @@
         <v>19.56</v>
       </c>
       <c r="M33">
-        <v>60.342399</v>
+        <v>62.28892800000001</v>
       </c>
       <c r="N33">
-        <v>-40.78239900000001</v>
+        <v>-42.72892800000001</v>
       </c>
       <c r="O33">
-        <v>-8.156479800000001</v>
+        <v>-8.545785600000002</v>
       </c>
       <c r="P33">
-        <v>-32.62591920000001</v>
+        <v>-34.18314240000001</v>
       </c>
       <c r="Q33">
-        <v>-24.18591920000001</v>
+        <v>-25.74314240000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1152339630740127</v>
+        <v>0.1162550507662775</v>
       </c>
       <c r="T33">
-        <v>1.353397177680014</v>
+        <v>1.373300077351779</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.06483003766555584</v>
+        <v>0.06280409898850722</v>
       </c>
       <c r="W33">
-        <v>0.2205130771184619</v>
+        <v>0.22099079345851</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4153,7 +4153,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3241501883277792</v>
+        <v>0.314020494942536</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1497704884277919</v>
+        <v>0.1516704884277919</v>
       </c>
       <c r="C34">
-        <v>121.0903008221402</v>
+        <v>106.0576370726103</v>
       </c>
       <c r="D34">
-        <v>377.6603008221402</v>
+        <v>370.8826370726104</v>
       </c>
       <c r="E34">
-        <v>186.36</v>
+        <v>194.615</v>
       </c>
       <c r="F34">
-        <v>264.16</v>
+        <v>272.415</v>
       </c>
       <c r="G34">
         <v>7.59</v>
@@ -4197,37 +4197,37 @@
         <v>19.56</v>
       </c>
       <c r="M34">
-        <v>62.28892800000001</v>
+        <v>64.23545700000001</v>
       </c>
       <c r="N34">
-        <v>-42.72892800000001</v>
+        <v>-44.67545700000002</v>
       </c>
       <c r="O34">
-        <v>-8.545785600000002</v>
+        <v>-8.935091400000003</v>
       </c>
       <c r="P34">
-        <v>-34.18314240000001</v>
+        <v>-35.74036560000001</v>
       </c>
       <c r="Q34">
-        <v>-25.74314240000001</v>
+        <v>-27.30036560000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1162550507662775</v>
+        <v>0.1173066186881623</v>
       </c>
       <c r="T34">
-        <v>1.373300077351779</v>
+        <v>1.393797093431656</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.06280409898850722</v>
+        <v>0.06090094447370396</v>
       </c>
       <c r="W34">
-        <v>0.22099079345851</v>
+        <v>0.2214395572931006</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4235,7 +4235,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.314020494942536</v>
+        <v>0.3045047223685198</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4243,22 +4243,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1516704884277919</v>
+        <v>0.1535704884277919</v>
       </c>
       <c r="C35">
-        <v>106.0576370726103</v>
+        <v>91.26395453791895</v>
       </c>
       <c r="D35">
-        <v>370.8826370726104</v>
+        <v>364.343954537919</v>
       </c>
       <c r="E35">
-        <v>194.615</v>
+        <v>202.87</v>
       </c>
       <c r="F35">
-        <v>272.415</v>
+        <v>280.67</v>
       </c>
       <c r="G35">
         <v>7.59</v>
@@ -4279,37 +4279,37 @@
         <v>19.56</v>
       </c>
       <c r="M35">
-        <v>64.23545700000001</v>
+        <v>66.18198600000001</v>
       </c>
       <c r="N35">
-        <v>-44.67545700000002</v>
+        <v>-46.62198600000001</v>
       </c>
       <c r="O35">
-        <v>-8.935091400000003</v>
+        <v>-9.324397200000003</v>
       </c>
       <c r="P35">
-        <v>-35.74036560000001</v>
+        <v>-37.29758880000001</v>
       </c>
       <c r="Q35">
-        <v>-27.30036560000001</v>
+        <v>-28.85758880000002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1173066186881623</v>
+        <v>0.1183900523046496</v>
       </c>
       <c r="T35">
-        <v>1.393797093431656</v>
+        <v>1.414915231210923</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.06090094447370396</v>
+        <v>0.05910974022447738</v>
       </c>
       <c r="W35">
-        <v>0.2214395572931006</v>
+        <v>0.2218619232550683</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3045047223685198</v>
+        <v>0.2955487011223868</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4325,22 +4325,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1535704884277919</v>
+        <v>0.1554704884277919</v>
       </c>
       <c r="C36">
-        <v>91.26395453791895</v>
+        <v>76.69683243883816</v>
       </c>
       <c r="D36">
-        <v>364.343954537919</v>
+        <v>358.0318324388382</v>
       </c>
       <c r="E36">
-        <v>202.87</v>
+        <v>211.125</v>
       </c>
       <c r="F36">
-        <v>280.67</v>
+        <v>288.925</v>
       </c>
       <c r="G36">
         <v>7.59</v>
@@ -4361,37 +4361,37 @@
         <v>19.56</v>
       </c>
       <c r="M36">
-        <v>66.18198600000001</v>
+        <v>68.12851500000001</v>
       </c>
       <c r="N36">
-        <v>-46.62198600000001</v>
+        <v>-48.56851500000001</v>
       </c>
       <c r="O36">
-        <v>-9.324397200000003</v>
+        <v>-9.713703000000002</v>
       </c>
       <c r="P36">
-        <v>-37.29758880000001</v>
+        <v>-38.85481200000001</v>
       </c>
       <c r="Q36">
-        <v>-28.85758880000002</v>
+        <v>-30.41481200000001</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1183900523046496</v>
+        <v>0.1195068223401057</v>
       </c>
       <c r="T36">
-        <v>1.414915231210923</v>
+        <v>1.436683157844937</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.05910974022447738</v>
+        <v>0.05742089050377802</v>
       </c>
       <c r="W36">
-        <v>0.2218619232550683</v>
+        <v>0.2222601540192091</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4399,7 +4399,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.2955487011223868</v>
+        <v>0.2871044525188902</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4407,22 +4407,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1554704884277919</v>
+        <v>0.1573704884277919</v>
       </c>
       <c r="C37">
-        <v>76.69683243883816</v>
+        <v>62.34469607939621</v>
       </c>
       <c r="D37">
-        <v>358.0318324388382</v>
+        <v>351.9346960793962</v>
       </c>
       <c r="E37">
-        <v>211.125</v>
+        <v>219.38</v>
       </c>
       <c r="F37">
-        <v>288.925</v>
+        <v>297.18</v>
       </c>
       <c r="G37">
         <v>7.59</v>
@@ -4443,37 +4443,37 @@
         <v>19.56</v>
       </c>
       <c r="M37">
-        <v>68.12851500000001</v>
+        <v>70.07504400000001</v>
       </c>
       <c r="N37">
-        <v>-48.56851500000001</v>
+        <v>-50.51504400000001</v>
       </c>
       <c r="O37">
-        <v>-9.713703000000002</v>
+        <v>-10.1030088</v>
       </c>
       <c r="P37">
-        <v>-38.85481200000001</v>
+        <v>-40.41203520000001</v>
       </c>
       <c r="Q37">
-        <v>-30.41481200000001</v>
+        <v>-31.97203520000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1195068223401057</v>
+        <v>0.1206584914391699</v>
       </c>
       <c r="T37">
-        <v>1.436683157844937</v>
+        <v>1.459131332186265</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.05742089050377802</v>
+        <v>0.05582586576756197</v>
       </c>
       <c r="W37">
-        <v>0.2222601540192091</v>
+        <v>0.2226362608520089</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2871044525188902</v>
+        <v>0.2791293288378098</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4489,22 +4489,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1573704884277919</v>
+        <v>0.1592704884277919</v>
       </c>
       <c r="C38">
-        <v>62.34469607939621</v>
+        <v>48.19674601091759</v>
       </c>
       <c r="D38">
-        <v>351.9346960793962</v>
+        <v>346.0417460109176</v>
       </c>
       <c r="E38">
-        <v>219.38</v>
+        <v>227.635</v>
       </c>
       <c r="F38">
-        <v>297.18</v>
+        <v>305.435</v>
       </c>
       <c r="G38">
         <v>7.59</v>
@@ -4525,37 +4525,37 @@
         <v>19.56</v>
       </c>
       <c r="M38">
-        <v>70.07504400000001</v>
+        <v>72.021573</v>
       </c>
       <c r="N38">
-        <v>-50.51504400000001</v>
+        <v>-52.46157300000001</v>
       </c>
       <c r="O38">
-        <v>-10.1030088</v>
+        <v>-10.4923146</v>
       </c>
       <c r="P38">
-        <v>-40.41203520000001</v>
+        <v>-41.96925840000001</v>
       </c>
       <c r="Q38">
-        <v>-31.97203520000001</v>
+        <v>-33.52925840000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1206584914391699</v>
+        <v>0.1218467214620138</v>
       </c>
       <c r="T38">
-        <v>1.459131332186265</v>
+        <v>1.482292146982872</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.05582586576756197</v>
+        <v>0.05431705858465489</v>
       </c>
       <c r="W38">
-        <v>0.2226362608520089</v>
+        <v>0.2229920375857384</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4563,7 +4563,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2791293288378098</v>
+        <v>0.2715852929232745</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4571,22 +4571,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1592704884277919</v>
+        <v>0.1611704884277919</v>
       </c>
       <c r="C39">
-        <v>48.19674601091759</v>
+        <v>34.24289419551383</v>
       </c>
       <c r="D39">
-        <v>346.0417460109176</v>
+        <v>340.3428941955138</v>
       </c>
       <c r="E39">
-        <v>227.635</v>
+        <v>235.89</v>
       </c>
       <c r="F39">
-        <v>305.435</v>
+        <v>313.69</v>
       </c>
       <c r="G39">
         <v>7.59</v>
@@ -4607,37 +4607,37 @@
         <v>19.56</v>
       </c>
       <c r="M39">
-        <v>72.021573</v>
+        <v>73.968102</v>
       </c>
       <c r="N39">
-        <v>-52.46157300000001</v>
+        <v>-54.40810200000001</v>
       </c>
       <c r="O39">
-        <v>-10.4923146</v>
+        <v>-10.8816204</v>
       </c>
       <c r="P39">
-        <v>-41.96925840000001</v>
+        <v>-43.5264816</v>
       </c>
       <c r="Q39">
-        <v>-33.52925840000001</v>
+        <v>-35.08648160000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1218467214620138</v>
+        <v>0.1230732814855947</v>
       </c>
       <c r="T39">
-        <v>1.482292146982872</v>
+        <v>1.506200084837434</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.05431705858465489</v>
+        <v>0.05288766230611134</v>
       </c>
       <c r="W39">
-        <v>0.2229920375857384</v>
+        <v>0.223329089228219</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2715852929232745</v>
+        <v>0.2644383115305567</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4653,22 +4653,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1611704884277919</v>
+        <v>0.1630704884277919</v>
       </c>
       <c r="C40">
-        <v>34.24289419551383</v>
+        <v>20.47370637519418</v>
       </c>
       <c r="D40">
-        <v>340.3428941955138</v>
+        <v>334.8287063751942</v>
       </c>
       <c r="E40">
-        <v>235.89</v>
+        <v>244.145</v>
       </c>
       <c r="F40">
-        <v>313.69</v>
+        <v>321.945</v>
       </c>
       <c r="G40">
         <v>7.59</v>
@@ -4689,37 +4689,37 @@
         <v>19.56</v>
       </c>
       <c r="M40">
-        <v>73.968102</v>
+        <v>75.914631</v>
       </c>
       <c r="N40">
-        <v>-54.40810200000001</v>
+        <v>-56.354631</v>
       </c>
       <c r="O40">
-        <v>-10.8816204</v>
+        <v>-11.2709262</v>
       </c>
       <c r="P40">
-        <v>-43.5264816</v>
+        <v>-45.08370480000001</v>
       </c>
       <c r="Q40">
-        <v>-35.08648160000001</v>
+        <v>-36.64370480000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1230732814855947</v>
+        <v>0.1243400565919159</v>
       </c>
       <c r="T40">
-        <v>1.506200084837434</v>
+        <v>1.530891889506901</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.05288766230611134</v>
+        <v>0.05153156840082643</v>
       </c>
       <c r="W40">
-        <v>0.223329089228219</v>
+        <v>0.2236488561710852</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4727,7 +4727,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2644383115305567</v>
+        <v>0.2576578420041322</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4735,22 +4735,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1630704884277919</v>
+        <v>0.1649704884277919</v>
       </c>
       <c r="C41">
-        <v>20.47370637519418</v>
+        <v>6.88034995402063</v>
       </c>
       <c r="D41">
-        <v>334.8287063751942</v>
+        <v>329.4903499540207</v>
       </c>
       <c r="E41">
-        <v>244.145</v>
+        <v>252.4</v>
       </c>
       <c r="F41">
-        <v>321.945</v>
+        <v>330.2</v>
       </c>
       <c r="G41">
         <v>7.59</v>
@@ -4771,37 +4771,37 @@
         <v>19.56</v>
       </c>
       <c r="M41">
-        <v>75.914631</v>
+        <v>77.86116000000001</v>
       </c>
       <c r="N41">
-        <v>-56.354631</v>
+        <v>-58.30116000000002</v>
       </c>
       <c r="O41">
-        <v>-11.2709262</v>
+        <v>-11.660232</v>
       </c>
       <c r="P41">
-        <v>-45.08370480000001</v>
+        <v>-46.64092800000002</v>
       </c>
       <c r="Q41">
-        <v>-36.64370480000001</v>
+        <v>-38.20092800000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1243400565919159</v>
+        <v>0.1256490575351145</v>
       </c>
       <c r="T41">
-        <v>1.530891889506901</v>
+        <v>1.556406754332015</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.05153156840082643</v>
+        <v>0.05024327919080577</v>
       </c>
       <c r="W41">
-        <v>0.2236488561710852</v>
+        <v>0.223952634766808</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2576578420041322</v>
+        <v>0.2512163959540289</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4817,22 +4817,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1649704884277919</v>
+        <v>0.166870488427792</v>
       </c>
       <c r="C42">
-        <v>6.88034995402063</v>
+        <v>-6.545453212318421</v>
       </c>
       <c r="D42">
-        <v>329.4903499540207</v>
+        <v>324.3195467876816</v>
       </c>
       <c r="E42">
-        <v>252.4</v>
+        <v>260.655</v>
       </c>
       <c r="F42">
-        <v>330.2</v>
+        <v>338.455</v>
       </c>
       <c r="G42">
         <v>7.59</v>
@@ -4853,37 +4853,37 @@
         <v>19.56</v>
       </c>
       <c r="M42">
-        <v>77.86116000000001</v>
+        <v>79.80768900000001</v>
       </c>
       <c r="N42">
-        <v>-58.30116000000002</v>
+        <v>-60.24768900000002</v>
       </c>
       <c r="O42">
-        <v>-11.660232</v>
+        <v>-12.0495378</v>
       </c>
       <c r="P42">
-        <v>-46.64092800000002</v>
+        <v>-48.19815120000001</v>
       </c>
       <c r="Q42">
-        <v>-38.20092800000002</v>
+        <v>-39.75815120000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1256490575351145</v>
+        <v>0.1270024313916419</v>
       </c>
       <c r="T42">
-        <v>1.556406754332015</v>
+        <v>1.582786529829168</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.05024327919080577</v>
+        <v>0.04901783335688368</v>
       </c>
       <c r="W42">
-        <v>0.223952634766808</v>
+        <v>0.2242415948944468</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2512163959540289</v>
+        <v>0.2450891667844184</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4899,22 +4899,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.166870488427792</v>
+        <v>0.1687704884277919</v>
       </c>
       <c r="C43">
-        <v>-6.545453212318421</v>
+        <v>-19.81146965028614</v>
       </c>
       <c r="D43">
-        <v>324.3195467876816</v>
+        <v>319.3085303497139</v>
       </c>
       <c r="E43">
-        <v>260.655</v>
+        <v>268.91</v>
       </c>
       <c r="F43">
-        <v>338.455</v>
+        <v>346.71</v>
       </c>
       <c r="G43">
         <v>7.59</v>
@@ -4935,37 +4935,37 @@
         <v>19.56</v>
       </c>
       <c r="M43">
-        <v>79.80768900000001</v>
+        <v>81.75421800000001</v>
       </c>
       <c r="N43">
-        <v>-60.24768900000002</v>
+        <v>-62.19421800000001</v>
       </c>
       <c r="O43">
-        <v>-12.0495378</v>
+        <v>-12.4388436</v>
       </c>
       <c r="P43">
-        <v>-48.19815120000001</v>
+        <v>-49.75537440000001</v>
       </c>
       <c r="Q43">
-        <v>-39.75815120000001</v>
+        <v>-41.31537440000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1270024313916419</v>
+        <v>0.1284024733121875</v>
       </c>
       <c r="T43">
-        <v>1.582786529829168</v>
+        <v>1.610075952757257</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.04901783335688368</v>
+        <v>0.04785074208648168</v>
       </c>
       <c r="W43">
-        <v>0.2242415948944468</v>
+        <v>0.2245167950160076</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2450891667844184</v>
+        <v>0.2392537104324084</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4981,22 +4981,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1687704884277919</v>
+        <v>0.1706704884277919</v>
       </c>
       <c r="C44">
-        <v>-19.81146965028603</v>
+        <v>-32.92499319178148</v>
       </c>
       <c r="D44">
-        <v>319.308530349714</v>
+        <v>314.4500068082185</v>
       </c>
       <c r="E44">
-        <v>268.91</v>
+        <v>277.165</v>
       </c>
       <c r="F44">
-        <v>346.71</v>
+        <v>354.965</v>
       </c>
       <c r="G44">
         <v>7.59</v>
@@ -5017,37 +5017,37 @@
         <v>19.56</v>
       </c>
       <c r="M44">
-        <v>81.75421799999999</v>
+        <v>83.70074699999999</v>
       </c>
       <c r="N44">
-        <v>-62.194218</v>
+        <v>-64.140747</v>
       </c>
       <c r="O44">
-        <v>-12.4388436</v>
+        <v>-12.8281494</v>
       </c>
       <c r="P44">
-        <v>-49.7553744</v>
+        <v>-51.3125976</v>
       </c>
       <c r="Q44">
-        <v>-41.3153744</v>
+        <v>-42.87259760000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1284024733121874</v>
+        <v>0.1298516395106469</v>
       </c>
       <c r="T44">
-        <v>1.610075952757257</v>
+        <v>1.638322899296858</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.0478507420864817</v>
+        <v>0.04673793413098212</v>
       </c>
       <c r="W44">
-        <v>0.2245167950160076</v>
+        <v>0.2247791951319144</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2392537104324085</v>
+        <v>0.2336896706549105</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5063,22 +5063,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1706704884277919</v>
+        <v>0.1725704884277919</v>
       </c>
       <c r="C45">
-        <v>-32.92499319178148</v>
+        <v>-45.89288039719708</v>
       </c>
       <c r="D45">
-        <v>314.4500068082185</v>
+        <v>309.737119602803</v>
       </c>
       <c r="E45">
-        <v>277.165</v>
+        <v>285.42</v>
       </c>
       <c r="F45">
-        <v>354.965</v>
+        <v>363.22</v>
       </c>
       <c r="G45">
         <v>7.59</v>
@@ -5099,37 +5099,37 @@
         <v>19.56</v>
       </c>
       <c r="M45">
-        <v>83.70074699999999</v>
+        <v>85.64727600000001</v>
       </c>
       <c r="N45">
-        <v>-64.140747</v>
+        <v>-66.087276</v>
       </c>
       <c r="O45">
-        <v>-12.8281494</v>
+        <v>-13.2174552</v>
       </c>
       <c r="P45">
-        <v>-51.3125976</v>
+        <v>-52.8698208</v>
       </c>
       <c r="Q45">
-        <v>-42.87259760000001</v>
+        <v>-44.4298208</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1298516395106469</v>
+        <v>0.1313525616447656</v>
       </c>
       <c r="T45">
-        <v>1.638322899296858</v>
+        <v>1.667578665355731</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.04673793413098212</v>
+        <v>0.04567570835527798</v>
       </c>
       <c r="W45">
-        <v>0.2247791951319144</v>
+        <v>0.2250296679698255</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5137,7 +5137,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2336896706549105</v>
+        <v>0.2283785417763899</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5145,22 +5145,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1725704884277919</v>
+        <v>0.1744704884277919</v>
       </c>
       <c r="C46">
-        <v>-45.89288039719708</v>
+        <v>-58.72158284005042</v>
       </c>
       <c r="D46">
-        <v>309.737119602803</v>
+        <v>305.1634171599496</v>
       </c>
       <c r="E46">
-        <v>285.42</v>
+        <v>293.675</v>
       </c>
       <c r="F46">
-        <v>363.22</v>
+        <v>371.475</v>
       </c>
       <c r="G46">
         <v>7.59</v>
@@ -5181,37 +5181,37 @@
         <v>19.56</v>
       </c>
       <c r="M46">
-        <v>85.64727600000001</v>
+        <v>87.593805</v>
       </c>
       <c r="N46">
-        <v>-66.087276</v>
+        <v>-68.033805</v>
       </c>
       <c r="O46">
-        <v>-13.2174552</v>
+        <v>-13.606761</v>
       </c>
       <c r="P46">
-        <v>-52.8698208</v>
+        <v>-54.427044</v>
       </c>
       <c r="Q46">
-        <v>-44.4298208</v>
+        <v>-45.987044</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1313525616447656</v>
+        <v>0.1329080627655795</v>
       </c>
       <c r="T46">
-        <v>1.667578665355731</v>
+        <v>1.697898277453108</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.04567570835527798</v>
+        <v>0.04466069261404958</v>
       </c>
       <c r="W46">
-        <v>0.2250296679698255</v>
+        <v>0.2252690086816071</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2283785417763899</v>
+        <v>0.223303463070248</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1744704884277919</v>
+        <v>0.1763704884277919</v>
       </c>
       <c r="C47">
-        <v>-58.72158284005042</v>
+        <v>-71.41717657287194</v>
       </c>
       <c r="D47">
-        <v>305.1634171599496</v>
+        <v>300.7228234271281</v>
       </c>
       <c r="E47">
-        <v>293.675</v>
+        <v>301.93</v>
       </c>
       <c r="F47">
-        <v>371.475</v>
+        <v>379.73</v>
       </c>
       <c r="G47">
         <v>7.59</v>
@@ -5263,37 +5263,37 @@
         <v>19.56</v>
       </c>
       <c r="M47">
-        <v>87.593805</v>
+        <v>89.540334</v>
       </c>
       <c r="N47">
-        <v>-68.033805</v>
+        <v>-69.980334</v>
       </c>
       <c r="O47">
-        <v>-13.606761</v>
+        <v>-13.9960668</v>
       </c>
       <c r="P47">
-        <v>-54.427044</v>
+        <v>-55.9842672</v>
       </c>
       <c r="Q47">
-        <v>-45.987044</v>
+        <v>-47.5442672</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1329080627655795</v>
+        <v>0.1345211750390161</v>
       </c>
       <c r="T47">
-        <v>1.697898277453108</v>
+        <v>1.729340838146684</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.04466069261404958</v>
+        <v>0.04368980799200502</v>
       </c>
       <c r="W47">
-        <v>0.2252690086816071</v>
+        <v>0.2254979432754852</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5301,7 +5301,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.223303463070248</v>
+        <v>0.2184490399600252</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5309,22 +5309,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1763704884277919</v>
+        <v>0.1782704884277919</v>
       </c>
       <c r="C48">
-        <v>-71.41717657287194</v>
+        <v>-83.98538905734915</v>
       </c>
       <c r="D48">
-        <v>300.7228234271281</v>
+        <v>296.4096109426509</v>
       </c>
       <c r="E48">
-        <v>301.93</v>
+        <v>310.185</v>
       </c>
       <c r="F48">
-        <v>379.73</v>
+        <v>387.985</v>
       </c>
       <c r="G48">
         <v>7.59</v>
@@ -5345,37 +5345,37 @@
         <v>19.56</v>
       </c>
       <c r="M48">
-        <v>89.540334</v>
+        <v>91.48686300000001</v>
       </c>
       <c r="N48">
-        <v>-69.980334</v>
+        <v>-71.92686300000003</v>
       </c>
       <c r="O48">
-        <v>-13.9960668</v>
+        <v>-14.38537260000001</v>
       </c>
       <c r="P48">
-        <v>-55.9842672</v>
+        <v>-57.54149040000002</v>
       </c>
       <c r="Q48">
-        <v>-47.5442672</v>
+        <v>-49.10149040000002</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1345211750390161</v>
+        <v>0.1361951594737145</v>
       </c>
       <c r="T48">
-        <v>1.729340838146684</v>
+        <v>1.761969910564546</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.04368980799200502</v>
+        <v>0.0427602376091964</v>
       </c>
       <c r="W48">
-        <v>0.2254979432754852</v>
+        <v>0.2257171359717515</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5383,7 +5383,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2184490399600252</v>
+        <v>0.2138011880459819</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5391,22 +5391,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1782704884277919</v>
+        <v>0.1801704884277919</v>
       </c>
       <c r="C49">
-        <v>-83.98538905734915</v>
+        <v>-96.43162380971569</v>
       </c>
       <c r="D49">
-        <v>296.4096109426509</v>
+        <v>292.2183761902843</v>
       </c>
       <c r="E49">
-        <v>310.185</v>
+        <v>318.44</v>
       </c>
       <c r="F49">
-        <v>387.985</v>
+        <v>396.24</v>
       </c>
       <c r="G49">
         <v>7.59</v>
@@ -5427,37 +5427,37 @@
         <v>19.56</v>
       </c>
       <c r="M49">
-        <v>91.48686300000001</v>
+        <v>93.43339200000001</v>
       </c>
       <c r="N49">
-        <v>-71.92686300000003</v>
+        <v>-73.87339200000002</v>
       </c>
       <c r="O49">
-        <v>-14.38537260000001</v>
+        <v>-14.77467840000001</v>
       </c>
       <c r="P49">
-        <v>-57.54149040000002</v>
+        <v>-59.09871360000002</v>
       </c>
       <c r="Q49">
-        <v>-49.10149040000002</v>
+        <v>-50.65871360000002</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1361951594737145</v>
+        <v>0.1379335279251321</v>
       </c>
       <c r="T49">
-        <v>1.761969910564546</v>
+        <v>1.795853947306172</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.0427602376091964</v>
+        <v>0.04186939932567148</v>
       </c>
       <c r="W49">
-        <v>0.2257171359717515</v>
+        <v>0.2259271956390067</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5465,7 +5465,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2138011880459819</v>
+        <v>0.2093469966283573</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5473,22 +5473,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1801704884277919</v>
+        <v>0.1820704884277919</v>
       </c>
       <c r="C50">
-        <v>-96.43162380971569</v>
+        <v>-108.7609829843784</v>
       </c>
       <c r="D50">
-        <v>292.2183761902843</v>
+        <v>288.1440170156216</v>
       </c>
       <c r="E50">
-        <v>318.44</v>
+        <v>326.695</v>
       </c>
       <c r="F50">
-        <v>396.24</v>
+        <v>404.495</v>
       </c>
       <c r="G50">
         <v>7.59</v>
@@ -5509,37 +5509,37 @@
         <v>19.56</v>
       </c>
       <c r="M50">
-        <v>93.43339200000001</v>
+        <v>95.37992100000001</v>
       </c>
       <c r="N50">
-        <v>-73.87339200000002</v>
+        <v>-75.81992100000002</v>
       </c>
       <c r="O50">
-        <v>-14.77467840000001</v>
+        <v>-15.16398420000001</v>
       </c>
       <c r="P50">
-        <v>-59.09871360000002</v>
+        <v>-60.65593680000002</v>
       </c>
       <c r="Q50">
-        <v>-50.65871360000002</v>
+        <v>-52.21593680000002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1379335279251321</v>
+        <v>0.13974006768837</v>
       </c>
       <c r="T50">
-        <v>1.795853947306172</v>
+        <v>1.831066769802371</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.04186939932567148</v>
+        <v>0.04101492178841287</v>
       </c>
       <c r="W50">
-        <v>0.2259271956390067</v>
+        <v>0.2261286814422923</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.2093469966283573</v>
+        <v>0.2050746089420643</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5555,22 +5555,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1820704884277919</v>
+        <v>0.1839704884277919</v>
       </c>
       <c r="C51">
-        <v>-108.7609829843784</v>
+        <v>-120.9782880942412</v>
       </c>
       <c r="D51">
-        <v>288.1440170156216</v>
+        <v>284.1817119057588</v>
       </c>
       <c r="E51">
-        <v>326.695</v>
+        <v>334.95</v>
       </c>
       <c r="F51">
-        <v>404.495</v>
+        <v>412.75</v>
       </c>
       <c r="G51">
         <v>7.59</v>
@@ -5591,37 +5591,37 @@
         <v>19.56</v>
       </c>
       <c r="M51">
-        <v>95.37992100000001</v>
+        <v>97.32645000000001</v>
       </c>
       <c r="N51">
-        <v>-75.81992100000002</v>
+        <v>-77.76645000000002</v>
       </c>
       <c r="O51">
-        <v>-15.16398420000001</v>
+        <v>-15.55329</v>
       </c>
       <c r="P51">
-        <v>-60.65593680000002</v>
+        <v>-62.21316000000002</v>
       </c>
       <c r="Q51">
-        <v>-52.21593680000002</v>
+        <v>-53.77316000000002</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.13974006768837</v>
+        <v>0.1416188690421374</v>
       </c>
       <c r="T51">
-        <v>1.831066769802371</v>
+        <v>1.867688105198419</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.04101492178841287</v>
+        <v>0.04019462335264462</v>
       </c>
       <c r="W51">
-        <v>0.2261286814422923</v>
+        <v>0.2263221078134464</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2050746089420643</v>
+        <v>0.200973116763223</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5637,22 +5637,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1839704884277919</v>
+        <v>0.1858704884277919</v>
       </c>
       <c r="C52">
-        <v>-120.9782880942412</v>
+        <v>-133.0880990446527</v>
       </c>
       <c r="D52">
-        <v>284.1817119057588</v>
+        <v>280.3269009553473</v>
       </c>
       <c r="E52">
-        <v>334.95</v>
+        <v>343.205</v>
       </c>
       <c r="F52">
-        <v>412.75</v>
+        <v>421.005</v>
       </c>
       <c r="G52">
         <v>7.59</v>
@@ -5673,37 +5673,37 @@
         <v>19.56</v>
       </c>
       <c r="M52">
-        <v>97.32645000000001</v>
+        <v>99.27297900000001</v>
       </c>
       <c r="N52">
-        <v>-77.76645000000002</v>
+        <v>-79.71297900000002</v>
       </c>
       <c r="O52">
-        <v>-15.55329</v>
+        <v>-15.9425958</v>
       </c>
       <c r="P52">
-        <v>-62.21316000000002</v>
+        <v>-63.77038320000001</v>
       </c>
       <c r="Q52">
-        <v>-53.77316000000002</v>
+        <v>-55.33038320000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1416188690421374</v>
+        <v>0.1435743561654464</v>
       </c>
       <c r="T52">
-        <v>1.867688105198419</v>
+        <v>1.905804188977978</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.04019462335264462</v>
+        <v>0.03940649348298492</v>
       </c>
       <c r="W52">
-        <v>0.2263221078134464</v>
+        <v>0.2265079488367122</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.200973116763223</v>
+        <v>0.1970324674149245</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5719,22 +5719,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1858704884277919</v>
+        <v>0.1877704884277919</v>
       </c>
       <c r="C53">
-        <v>-133.0880990446527</v>
+        <v>-145.0947316389581</v>
       </c>
       <c r="D53">
-        <v>280.3269009553473</v>
+        <v>276.5752683610419</v>
       </c>
       <c r="E53">
-        <v>343.205</v>
+        <v>351.46</v>
       </c>
       <c r="F53">
-        <v>421.005</v>
+        <v>429.26</v>
       </c>
       <c r="G53">
         <v>7.59</v>
@@ -5755,37 +5755,37 @@
         <v>19.56</v>
       </c>
       <c r="M53">
-        <v>99.27297900000001</v>
+        <v>101.219508</v>
       </c>
       <c r="N53">
-        <v>-79.71297900000002</v>
+        <v>-81.65950800000002</v>
       </c>
       <c r="O53">
-        <v>-15.9425958</v>
+        <v>-16.33190160000001</v>
       </c>
       <c r="P53">
-        <v>-63.77038320000001</v>
+        <v>-65.32760640000001</v>
       </c>
       <c r="Q53">
-        <v>-55.33038320000001</v>
+        <v>-56.88760640000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1435743561654464</v>
+        <v>0.1456113219188931</v>
       </c>
       <c r="T53">
-        <v>1.905804188977978</v>
+        <v>1.945508442915019</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.03940649348298492</v>
+        <v>0.03864867630061983</v>
       </c>
       <c r="W53">
-        <v>0.2265079488367122</v>
+        <v>0.2266866421283139</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1970324674149245</v>
+        <v>0.1932433815030991</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5801,22 +5801,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1877704884277919</v>
+        <v>0.1896704884277919</v>
       </c>
       <c r="C54">
-        <v>-145.0947316389581</v>
+        <v>-157.0022736969476</v>
       </c>
       <c r="D54">
-        <v>276.5752683610419</v>
+        <v>272.9227263030525</v>
       </c>
       <c r="E54">
-        <v>351.46</v>
+        <v>359.715</v>
       </c>
       <c r="F54">
-        <v>429.26</v>
+        <v>437.515</v>
       </c>
       <c r="G54">
         <v>7.59</v>
@@ -5837,37 +5837,37 @@
         <v>19.56</v>
       </c>
       <c r="M54">
-        <v>101.219508</v>
+        <v>103.166037</v>
       </c>
       <c r="N54">
-        <v>-81.65950800000002</v>
+        <v>-83.60603700000001</v>
       </c>
       <c r="O54">
-        <v>-16.33190160000001</v>
+        <v>-16.7212074</v>
       </c>
       <c r="P54">
-        <v>-65.32760640000001</v>
+        <v>-66.88482960000002</v>
       </c>
       <c r="Q54">
-        <v>-56.88760640000001</v>
+        <v>-58.44482960000002</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1456113219188931</v>
+        <v>0.1477349670661037</v>
       </c>
       <c r="T54">
-        <v>1.945508442915019</v>
+        <v>1.986902239572786</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.03864867630061983</v>
+        <v>0.03791945599306096</v>
       </c>
       <c r="W54">
-        <v>0.2266866421283139</v>
+        <v>0.2268585922768362</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1932433815030991</v>
+        <v>0.1895972799653048</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5883,22 +5883,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1896704884277919</v>
+        <v>0.191570488427792</v>
       </c>
       <c r="C55">
-        <v>-157.0022736969476</v>
+        <v>-168.8145999127589</v>
       </c>
       <c r="D55">
-        <v>272.9227263030525</v>
+        <v>269.3654000872412</v>
       </c>
       <c r="E55">
-        <v>359.715</v>
+        <v>367.97</v>
       </c>
       <c r="F55">
-        <v>437.515</v>
+        <v>445.77</v>
       </c>
       <c r="G55">
         <v>7.59</v>
@@ -5919,37 +5919,37 @@
         <v>19.56</v>
       </c>
       <c r="M55">
-        <v>103.166037</v>
+        <v>105.112566</v>
       </c>
       <c r="N55">
-        <v>-83.60603700000001</v>
+        <v>-85.55256600000001</v>
       </c>
       <c r="O55">
-        <v>-16.7212074</v>
+        <v>-17.1105132</v>
       </c>
       <c r="P55">
-        <v>-66.88482960000002</v>
+        <v>-68.44205280000001</v>
       </c>
       <c r="Q55">
-        <v>-58.44482960000002</v>
+        <v>-60.00205280000002</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1477349670661037</v>
+        <v>0.149950944611019</v>
       </c>
       <c r="T55">
-        <v>1.986902239572786</v>
+        <v>2.030095766520021</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.03791945599306096</v>
+        <v>0.03721724384504131</v>
       </c>
       <c r="W55">
-        <v>0.2268585922768362</v>
+        <v>0.2270241739013393</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1895972799653048</v>
+        <v>0.1860862192252066</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5965,22 +5965,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.191570488427792</v>
+        <v>0.1934704884277919</v>
       </c>
       <c r="C56">
-        <v>-168.8145999127589</v>
+        <v>-180.535385565767</v>
       </c>
       <c r="D56">
-        <v>269.3654000872412</v>
+        <v>265.8996144342331</v>
       </c>
       <c r="E56">
-        <v>367.97</v>
+        <v>376.225</v>
       </c>
       <c r="F56">
-        <v>445.77</v>
+        <v>454.025</v>
       </c>
       <c r="G56">
         <v>7.59</v>
@@ -6001,37 +6001,37 @@
         <v>19.56</v>
       </c>
       <c r="M56">
-        <v>105.112566</v>
+        <v>107.059095</v>
       </c>
       <c r="N56">
-        <v>-85.55256600000001</v>
+        <v>-87.49909500000001</v>
       </c>
       <c r="O56">
-        <v>-17.1105132</v>
+        <v>-17.499819</v>
       </c>
       <c r="P56">
-        <v>-68.44205280000001</v>
+        <v>-69.99927600000001</v>
       </c>
       <c r="Q56">
-        <v>-60.00205280000002</v>
+        <v>-61.55927600000001</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.149950944611019</v>
+        <v>0.1522654100468194</v>
       </c>
       <c r="T56">
-        <v>2.030095766520021</v>
+        <v>2.075209005776021</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.03721724384504131</v>
+        <v>0.03654056668422238</v>
       </c>
       <c r="W56">
-        <v>0.2270241739013393</v>
+        <v>0.2271837343758604</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6039,7 +6039,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1860862192252066</v>
+        <v>0.1827028334211119</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6047,22 +6047,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1934704884277919</v>
+        <v>0.1953704884277919</v>
       </c>
       <c r="C57">
-        <v>-180.535385565767</v>
+        <v>-192.1681191864535</v>
       </c>
       <c r="D57">
-        <v>265.8996144342331</v>
+        <v>262.5218808135465</v>
       </c>
       <c r="E57">
-        <v>376.225</v>
+        <v>384.48</v>
       </c>
       <c r="F57">
-        <v>454.025</v>
+        <v>462.28</v>
       </c>
       <c r="G57">
         <v>7.59</v>
@@ -6083,37 +6083,37 @@
         <v>19.56</v>
       </c>
       <c r="M57">
-        <v>107.059095</v>
+        <v>109.005624</v>
       </c>
       <c r="N57">
-        <v>-87.49909500000001</v>
+        <v>-89.44562400000001</v>
       </c>
       <c r="O57">
-        <v>-17.499819</v>
+        <v>-17.8891248</v>
       </c>
       <c r="P57">
-        <v>-69.99927600000001</v>
+        <v>-71.5564992</v>
       </c>
       <c r="Q57">
-        <v>-61.55927600000001</v>
+        <v>-63.11649920000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1522654100468194</v>
+        <v>0.1546850784569744</v>
       </c>
       <c r="T57">
-        <v>2.075209005776021</v>
+        <v>2.122372846816385</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.03654056668422238</v>
+        <v>0.03588805656486126</v>
       </c>
       <c r="W57">
-        <v>0.2271837343758604</v>
+        <v>0.2273375962620057</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1827028334211119</v>
+        <v>0.1794402828243064</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6129,22 +6129,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1953704884277919</v>
+        <v>0.1972704884277919</v>
       </c>
       <c r="C58">
-        <v>-192.1681191864535</v>
+        <v>-203.7161142690139</v>
       </c>
       <c r="D58">
-        <v>262.5218808135465</v>
+        <v>259.2288857309862</v>
       </c>
       <c r="E58">
-        <v>384.48</v>
+        <v>392.735</v>
       </c>
       <c r="F58">
-        <v>462.28</v>
+        <v>470.535</v>
       </c>
       <c r="G58">
         <v>7.59</v>
@@ -6165,37 +6165,37 @@
         <v>19.56</v>
       </c>
       <c r="M58">
-        <v>109.005624</v>
+        <v>110.952153</v>
       </c>
       <c r="N58">
-        <v>-89.44562400000001</v>
+        <v>-91.39215300000001</v>
       </c>
       <c r="O58">
-        <v>-17.8891248</v>
+        <v>-18.2784306</v>
       </c>
       <c r="P58">
-        <v>-71.5564992</v>
+        <v>-73.1137224</v>
       </c>
       <c r="Q58">
-        <v>-63.11649920000001</v>
+        <v>-64.6737224</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1546850784569744</v>
+        <v>0.1572172895838808</v>
       </c>
       <c r="T58">
-        <v>2.122372846816385</v>
+        <v>2.171730354881882</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.03588805656486126</v>
+        <v>0.03525844153740756</v>
       </c>
       <c r="W58">
-        <v>0.2273375962620057</v>
+        <v>0.2274860594854793</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1794402828243064</v>
+        <v>0.1762922076870379</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6211,22 +6211,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1972704884277919</v>
+        <v>0.1991704884277919</v>
       </c>
       <c r="C59">
-        <v>-203.7161142690139</v>
+        <v>-215.1825201133708</v>
       </c>
       <c r="D59">
-        <v>259.2288857309862</v>
+        <v>256.0174798866293</v>
       </c>
       <c r="E59">
-        <v>392.735</v>
+        <v>400.9900000000001</v>
       </c>
       <c r="F59">
-        <v>470.535</v>
+        <v>478.7900000000001</v>
       </c>
       <c r="G59">
         <v>7.59</v>
@@ -6247,37 +6247,37 @@
         <v>19.56</v>
       </c>
       <c r="M59">
-        <v>110.952153</v>
+        <v>112.898682</v>
       </c>
       <c r="N59">
-        <v>-91.39215300000001</v>
+        <v>-93.33868200000003</v>
       </c>
       <c r="O59">
-        <v>-18.2784306</v>
+        <v>-18.66773640000001</v>
       </c>
       <c r="P59">
-        <v>-73.1137224</v>
+        <v>-74.67094560000002</v>
       </c>
       <c r="Q59">
-        <v>-64.6737224</v>
+        <v>-66.23094560000003</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1572172895838808</v>
+        <v>0.1598700821930208</v>
       </c>
       <c r="T59">
-        <v>2.171730354881882</v>
+        <v>2.223438220474308</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.03525844153740756</v>
+        <v>0.03465053737296949</v>
       </c>
       <c r="W59">
-        <v>0.2274860594854793</v>
+        <v>0.2276294032874538</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6285,7 +6285,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1762922076870379</v>
+        <v>0.1732526868648474</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1991704884277919</v>
+        <v>0.2010704884277919</v>
       </c>
       <c r="C60">
-        <v>-215.1825201133706</v>
+        <v>-226.5703318711619</v>
       </c>
       <c r="D60">
-        <v>256.0174798866294</v>
+        <v>252.8846681288381</v>
       </c>
       <c r="E60">
-        <v>400.99</v>
+        <v>409.2449999999999</v>
       </c>
       <c r="F60">
-        <v>478.79</v>
+        <v>487.045</v>
       </c>
       <c r="G60">
         <v>7.59</v>
@@ -6329,37 +6329,37 @@
         <v>19.56</v>
       </c>
       <c r="M60">
-        <v>112.898682</v>
+        <v>114.845211</v>
       </c>
       <c r="N60">
-        <v>-93.33868200000001</v>
+        <v>-95.285211</v>
       </c>
       <c r="O60">
-        <v>-18.6677364</v>
+        <v>-19.0570422</v>
       </c>
       <c r="P60">
-        <v>-74.67094560000001</v>
+        <v>-76.22816880000001</v>
       </c>
       <c r="Q60">
-        <v>-66.23094560000001</v>
+        <v>-67.78816880000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1598700821930207</v>
+        <v>0.1626522793196798</v>
       </c>
       <c r="T60">
-        <v>2.223438220474308</v>
+        <v>2.277668420973681</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0346505373729695</v>
+        <v>0.03406324012935985</v>
       </c>
       <c r="W60">
-        <v>0.2276294032874538</v>
+        <v>0.2277678879774969</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6367,7 +6367,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1732526868648474</v>
+        <v>0.1703162006467992</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6375,22 +6375,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2010704884277919</v>
+        <v>0.2029704884277919</v>
       </c>
       <c r="C61">
-        <v>-226.5703318711619</v>
+        <v>-237.8823998630677</v>
       </c>
       <c r="D61">
-        <v>252.8846681288381</v>
+        <v>249.8276001369323</v>
       </c>
       <c r="E61">
-        <v>409.2449999999999</v>
+        <v>417.4999999999999</v>
       </c>
       <c r="F61">
-        <v>487.045</v>
+        <v>495.3</v>
       </c>
       <c r="G61">
         <v>7.59</v>
@@ -6411,37 +6411,37 @@
         <v>19.56</v>
       </c>
       <c r="M61">
-        <v>114.845211</v>
+        <v>116.79174</v>
       </c>
       <c r="N61">
-        <v>-95.285211</v>
+        <v>-97.23174</v>
       </c>
       <c r="O61">
-        <v>-19.0570422</v>
+        <v>-19.446348</v>
       </c>
       <c r="P61">
-        <v>-76.22816880000001</v>
+        <v>-77.785392</v>
       </c>
       <c r="Q61">
-        <v>-67.78816880000001</v>
+        <v>-69.345392</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1626522793196798</v>
+        <v>0.1655735863026718</v>
       </c>
       <c r="T61">
-        <v>2.277668420973681</v>
+        <v>2.334610131498023</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.03406324012935985</v>
+        <v>0.03349551946053719</v>
       </c>
       <c r="W61">
-        <v>0.2277678879774969</v>
+        <v>0.2279017565112053</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1703162006467992</v>
+        <v>0.1674775973026859</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6457,22 +6457,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2029704884277919</v>
+        <v>0.2048704884277919</v>
       </c>
       <c r="C62">
-        <v>-237.8823998630677</v>
+        <v>-249.1214382283969</v>
       </c>
       <c r="D62">
-        <v>249.8276001369323</v>
+        <v>246.8435617716031</v>
       </c>
       <c r="E62">
-        <v>417.4999999999999</v>
+        <v>425.755</v>
       </c>
       <c r="F62">
-        <v>495.3</v>
+        <v>503.555</v>
       </c>
       <c r="G62">
         <v>7.59</v>
@@ -6493,37 +6493,37 @@
         <v>19.56</v>
       </c>
       <c r="M62">
-        <v>116.79174</v>
+        <v>118.738269</v>
       </c>
       <c r="N62">
-        <v>-97.23174</v>
+        <v>-99.178269</v>
       </c>
       <c r="O62">
-        <v>-19.446348</v>
+        <v>-19.8356538</v>
       </c>
       <c r="P62">
-        <v>-77.785392</v>
+        <v>-79.3426152</v>
       </c>
       <c r="Q62">
-        <v>-69.345392</v>
+        <v>-70.9026152</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1655735863026718</v>
+        <v>0.1686447039001762</v>
       </c>
       <c r="T62">
-        <v>2.334610131498023</v>
+        <v>2.394471929741562</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.03349551946053719</v>
+        <v>0.03294641258413494</v>
       </c>
       <c r="W62">
-        <v>0.2279017565112053</v>
+        <v>0.228031235912661</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1674775973026859</v>
+        <v>0.1647320629206748</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6539,22 +6539,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2048704884277919</v>
+        <v>0.2067704884277919</v>
       </c>
       <c r="C63">
-        <v>-249.1214382283969</v>
+        <v>-260.2900329621075</v>
       </c>
       <c r="D63">
-        <v>246.8435617716031</v>
+        <v>243.9299670378925</v>
       </c>
       <c r="E63">
-        <v>425.755</v>
+        <v>434.01</v>
       </c>
       <c r="F63">
-        <v>503.555</v>
+        <v>511.81</v>
       </c>
       <c r="G63">
         <v>7.59</v>
@@ -6575,37 +6575,37 @@
         <v>19.56</v>
       </c>
       <c r="M63">
-        <v>118.738269</v>
+        <v>120.684798</v>
       </c>
       <c r="N63">
-        <v>-99.178269</v>
+        <v>-101.124798</v>
       </c>
       <c r="O63">
-        <v>-19.8356538</v>
+        <v>-20.2249596</v>
       </c>
       <c r="P63">
-        <v>-79.3426152</v>
+        <v>-80.89983839999999</v>
       </c>
       <c r="Q63">
-        <v>-70.9026152</v>
+        <v>-72.4598384</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1686447039001762</v>
+        <v>0.1718774592659703</v>
       </c>
       <c r="T63">
-        <v>2.394471929741562</v>
+        <v>2.457484348945288</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.03294641258413494</v>
+        <v>0.03241501883277792</v>
       </c>
       <c r="W63">
-        <v>0.228031235912661</v>
+        <v>0.228156538559231</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1647320629206748</v>
+        <v>0.1620750941638897</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6621,22 +6621,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2067704884277919</v>
+        <v>0.208670488427792</v>
       </c>
       <c r="C64">
-        <v>-260.2900329621075</v>
+        <v>-271.3906493892817</v>
       </c>
       <c r="D64">
-        <v>243.9299670378925</v>
+        <v>241.0843506107183</v>
       </c>
       <c r="E64">
-        <v>434.01</v>
+        <v>442.265</v>
       </c>
       <c r="F64">
-        <v>511.81</v>
+        <v>520.0650000000001</v>
       </c>
       <c r="G64">
         <v>7.59</v>
@@ -6657,37 +6657,37 @@
         <v>19.56</v>
       </c>
       <c r="M64">
-        <v>120.684798</v>
+        <v>122.631327</v>
       </c>
       <c r="N64">
-        <v>-101.124798</v>
+        <v>-103.071327</v>
       </c>
       <c r="O64">
-        <v>-20.2249596</v>
+        <v>-20.61426540000001</v>
       </c>
       <c r="P64">
-        <v>-80.89983839999999</v>
+        <v>-82.45706160000002</v>
       </c>
       <c r="Q64">
-        <v>-72.4598384</v>
+        <v>-74.01706160000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1718774592659703</v>
+        <v>0.1752849581650506</v>
       </c>
       <c r="T64">
-        <v>2.457484348945288</v>
+        <v>2.523902844862728</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.03241501883277792</v>
+        <v>0.03190049472432113</v>
       </c>
       <c r="W64">
-        <v>0.228156538559231</v>
+        <v>0.2282778633440051</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6695,7 +6695,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1620750941638897</v>
+        <v>0.1595024736216055</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6703,22 +6703,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.208670488427792</v>
+        <v>0.2105704884277919</v>
       </c>
       <c r="C65">
-        <v>-271.3906493892817</v>
+        <v>-282.4256391224619</v>
       </c>
       <c r="D65">
-        <v>241.0843506107183</v>
+        <v>238.3043608775381</v>
       </c>
       <c r="E65">
-        <v>442.265</v>
+        <v>450.52</v>
       </c>
       <c r="F65">
-        <v>520.0650000000001</v>
+        <v>528.3200000000001</v>
       </c>
       <c r="G65">
         <v>7.59</v>
@@ -6739,37 +6739,37 @@
         <v>19.56</v>
       </c>
       <c r="M65">
-        <v>122.631327</v>
+        <v>124.577856</v>
       </c>
       <c r="N65">
-        <v>-103.071327</v>
+        <v>-105.017856</v>
       </c>
       <c r="O65">
-        <v>-20.61426540000001</v>
+        <v>-21.00357120000001</v>
       </c>
       <c r="P65">
-        <v>-82.45706160000002</v>
+        <v>-84.01428480000001</v>
       </c>
       <c r="Q65">
-        <v>-74.01706160000002</v>
+        <v>-75.57428480000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1752849581650506</v>
+        <v>0.1788817625585242</v>
       </c>
       <c r="T65">
-        <v>2.523902844862728</v>
+        <v>2.594011257220026</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.03190049472432113</v>
+        <v>0.03140204949425361</v>
       </c>
       <c r="W65">
-        <v>0.2282778633440051</v>
+        <v>0.228395396729255</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6777,7 +6777,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1595024736216055</v>
+        <v>0.157010247471268</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6785,22 +6785,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2105704884277919</v>
+        <v>0.2124704884277919</v>
       </c>
       <c r="C66">
-        <v>-282.4256391224619</v>
+        <v>-293.3972465431181</v>
       </c>
       <c r="D66">
-        <v>238.3043608775381</v>
+        <v>235.587753456882</v>
       </c>
       <c r="E66">
-        <v>450.52</v>
+        <v>458.775</v>
       </c>
       <c r="F66">
-        <v>528.3200000000001</v>
+        <v>536.575</v>
       </c>
       <c r="G66">
         <v>7.59</v>
@@ -6821,37 +6821,37 @@
         <v>19.56</v>
       </c>
       <c r="M66">
-        <v>124.577856</v>
+        <v>126.524385</v>
       </c>
       <c r="N66">
-        <v>-105.017856</v>
+        <v>-106.964385</v>
       </c>
       <c r="O66">
-        <v>-21.00357120000001</v>
+        <v>-21.39287700000001</v>
       </c>
       <c r="P66">
-        <v>-84.01428480000001</v>
+        <v>-85.57150800000002</v>
       </c>
       <c r="Q66">
-        <v>-75.57428480000002</v>
+        <v>-77.13150800000003</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1788817625585242</v>
+        <v>0.1826840986316249</v>
       </c>
       <c r="T66">
-        <v>2.594011257220026</v>
+        <v>2.66812586456917</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.03140204949425361</v>
+        <v>0.03091894104049586</v>
       </c>
       <c r="W66">
-        <v>0.228395396729255</v>
+        <v>0.2285093137026511</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.157010247471268</v>
+        <v>0.1545947052024792</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6867,22 +6867,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2124704884277919</v>
+        <v>0.2143704884277919</v>
       </c>
       <c r="C67">
-        <v>-293.3972465431181</v>
+        <v>-304.3076148447875</v>
       </c>
       <c r="D67">
-        <v>235.587753456882</v>
+        <v>232.9323851552126</v>
       </c>
       <c r="E67">
-        <v>458.775</v>
+        <v>467.03</v>
       </c>
       <c r="F67">
-        <v>536.575</v>
+        <v>544.83</v>
       </c>
       <c r="G67">
         <v>7.59</v>
@@ -6903,37 +6903,37 @@
         <v>19.56</v>
       </c>
       <c r="M67">
-        <v>126.524385</v>
+        <v>128.470914</v>
       </c>
       <c r="N67">
-        <v>-106.964385</v>
+        <v>-108.910914</v>
       </c>
       <c r="O67">
-        <v>-21.39287700000001</v>
+        <v>-21.7821828</v>
       </c>
       <c r="P67">
-        <v>-85.57150800000002</v>
+        <v>-87.12873120000002</v>
       </c>
       <c r="Q67">
-        <v>-77.13150800000003</v>
+        <v>-78.68873120000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1826840986316249</v>
+        <v>0.1867101015325551</v>
       </c>
       <c r="T67">
-        <v>2.66812586456917</v>
+        <v>2.746600154703557</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03091894104049586</v>
+        <v>0.03045047223685198</v>
       </c>
       <c r="W67">
-        <v>0.2285093137026511</v>
+        <v>0.2286197786465503</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6941,7 +6941,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1545947052024792</v>
+        <v>0.15225236118426</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6949,22 +6949,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2143704884277919</v>
+        <v>0.2162704884277919</v>
       </c>
       <c r="C68">
-        <v>-304.3076148447875</v>
+        <v>-315.1587916720883</v>
       </c>
       <c r="D68">
-        <v>232.9323851552126</v>
+        <v>230.3362083279117</v>
       </c>
       <c r="E68">
-        <v>467.03</v>
+        <v>475.285</v>
       </c>
       <c r="F68">
-        <v>544.83</v>
+        <v>553.085</v>
       </c>
       <c r="G68">
         <v>7.59</v>
@@ -6985,37 +6985,37 @@
         <v>19.56</v>
       </c>
       <c r="M68">
-        <v>128.470914</v>
+        <v>130.417443</v>
       </c>
       <c r="N68">
-        <v>-108.910914</v>
+        <v>-110.857443</v>
       </c>
       <c r="O68">
-        <v>-21.7821828</v>
+        <v>-22.1714886</v>
       </c>
       <c r="P68">
-        <v>-87.12873120000002</v>
+        <v>-88.68595440000001</v>
       </c>
       <c r="Q68">
-        <v>-78.68873120000002</v>
+        <v>-80.24595440000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1867101015325551</v>
+        <v>0.1909801046092992</v>
       </c>
       <c r="T68">
-        <v>2.746600154703557</v>
+        <v>2.829830462421846</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03045047223685198</v>
+        <v>0.02999598757660046</v>
       </c>
       <c r="W68">
-        <v>0.2286197786465503</v>
+        <v>0.2287269461294376</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.15225236118426</v>
+        <v>0.1499799378830023</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7031,22 +7031,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2162704884277919</v>
+        <v>0.2181704884277919</v>
       </c>
       <c r="C69">
-        <v>-315.1587916720883</v>
+        <v>-325.9527343867884</v>
       </c>
       <c r="D69">
-        <v>230.3362083279117</v>
+        <v>227.7972656132116</v>
       </c>
       <c r="E69">
-        <v>475.285</v>
+        <v>483.54</v>
       </c>
       <c r="F69">
-        <v>553.085</v>
+        <v>561.34</v>
       </c>
       <c r="G69">
         <v>7.59</v>
@@ -7067,37 +7067,37 @@
         <v>19.56</v>
       </c>
       <c r="M69">
-        <v>130.417443</v>
+        <v>132.363972</v>
       </c>
       <c r="N69">
-        <v>-110.857443</v>
+        <v>-112.803972</v>
       </c>
       <c r="O69">
-        <v>-22.1714886</v>
+        <v>-22.56079440000001</v>
       </c>
       <c r="P69">
-        <v>-88.68595440000001</v>
+        <v>-90.24317760000001</v>
       </c>
       <c r="Q69">
-        <v>-80.24595440000002</v>
+        <v>-81.80317760000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1909801046092992</v>
+        <v>0.1955169828783398</v>
       </c>
       <c r="T69">
-        <v>2.829830462421846</v>
+        <v>2.91826266437253</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.02999598757660046</v>
+        <v>0.02955487011223869</v>
       </c>
       <c r="W69">
-        <v>0.2287269461294376</v>
+        <v>0.2288309616275341</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7105,7 +7105,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1499799378830023</v>
+        <v>0.1477743505611935</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7113,22 +7113,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2181704884277919</v>
+        <v>0.2200704884277919</v>
       </c>
       <c r="C70">
-        <v>-325.9527343867884</v>
+        <v>-336.6913149893896</v>
       </c>
       <c r="D70">
-        <v>227.7972656132116</v>
+        <v>225.3136850106104</v>
       </c>
       <c r="E70">
-        <v>483.54</v>
+        <v>491.795</v>
       </c>
       <c r="F70">
-        <v>561.34</v>
+        <v>569.595</v>
       </c>
       <c r="G70">
         <v>7.59</v>
@@ -7149,37 +7149,37 @@
         <v>19.56</v>
       </c>
       <c r="M70">
-        <v>132.363972</v>
+        <v>134.310501</v>
       </c>
       <c r="N70">
-        <v>-112.803972</v>
+        <v>-114.750501</v>
       </c>
       <c r="O70">
-        <v>-22.56079440000001</v>
+        <v>-22.9501002</v>
       </c>
       <c r="P70">
-        <v>-90.24317760000001</v>
+        <v>-91.80040080000001</v>
       </c>
       <c r="Q70">
-        <v>-81.80317760000001</v>
+        <v>-83.36040080000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1955169828783398</v>
+        <v>0.2003465629711895</v>
       </c>
       <c r="T70">
-        <v>2.91826266437253</v>
+        <v>3.01240016967487</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.02955487011223869</v>
+        <v>0.02912653866133668</v>
       </c>
       <c r="W70">
-        <v>0.2288309616275341</v>
+        <v>0.2289319621836568</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1477743505611935</v>
+        <v>0.1456326933066835</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7195,22 +7195,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2200704884277919</v>
+        <v>0.2219704884277919</v>
       </c>
       <c r="C71">
-        <v>-336.6913149893896</v>
+        <v>-347.3763247222378</v>
       </c>
       <c r="D71">
-        <v>225.3136850106104</v>
+        <v>222.8836752777622</v>
       </c>
       <c r="E71">
-        <v>491.795</v>
+        <v>500.05</v>
       </c>
       <c r="F71">
-        <v>569.595</v>
+        <v>577.85</v>
       </c>
       <c r="G71">
         <v>7.59</v>
@@ -7231,37 +7231,37 @@
         <v>19.56</v>
       </c>
       <c r="M71">
-        <v>134.310501</v>
+        <v>136.25703</v>
       </c>
       <c r="N71">
-        <v>-114.750501</v>
+        <v>-116.69703</v>
       </c>
       <c r="O71">
-        <v>-22.9501002</v>
+        <v>-23.339406</v>
       </c>
       <c r="P71">
-        <v>-91.80040080000001</v>
+        <v>-93.35762400000002</v>
       </c>
       <c r="Q71">
-        <v>-83.36040080000001</v>
+        <v>-84.91762400000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2003465629711895</v>
+        <v>0.2054981150702291</v>
       </c>
       <c r="T71">
-        <v>3.01240016967487</v>
+        <v>3.112813508664031</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.02912653866133668</v>
+        <v>0.02871044525188901</v>
       </c>
       <c r="W71">
-        <v>0.2289319621836568</v>
+        <v>0.2290300770096046</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1456326933066835</v>
+        <v>0.1435522262594451</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7277,22 +7277,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2219704884277919</v>
+        <v>0.2238704884277919</v>
       </c>
       <c r="C72">
-        <v>-347.3763247222378</v>
+        <v>-358.0094783779429</v>
       </c>
       <c r="D72">
-        <v>222.8836752777622</v>
+        <v>220.5055216220571</v>
       </c>
       <c r="E72">
-        <v>500.05</v>
+        <v>508.305</v>
       </c>
       <c r="F72">
-        <v>577.85</v>
+        <v>586.105</v>
       </c>
       <c r="G72">
         <v>7.59</v>
@@ -7313,37 +7313,37 @@
         <v>19.56</v>
       </c>
       <c r="M72">
-        <v>136.25703</v>
+        <v>138.203559</v>
       </c>
       <c r="N72">
-        <v>-116.69703</v>
+        <v>-118.643559</v>
       </c>
       <c r="O72">
-        <v>-23.339406</v>
+        <v>-23.7287118</v>
       </c>
       <c r="P72">
-        <v>-93.35762400000002</v>
+        <v>-94.91484720000001</v>
       </c>
       <c r="Q72">
-        <v>-84.91762400000002</v>
+        <v>-86.47484720000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2054981150702291</v>
+        <v>0.2110049466243749</v>
       </c>
       <c r="T72">
-        <v>3.112813508664031</v>
+        <v>3.220151905514516</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.02871044525188901</v>
+        <v>0.02830607278355255</v>
       </c>
       <c r="W72">
-        <v>0.2290300770096046</v>
+        <v>0.2291254280376383</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1435522262594451</v>
+        <v>0.1415303639177627</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7359,22 +7359,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2238704884277919</v>
+        <v>0.2257704884277919</v>
       </c>
       <c r="C73">
-        <v>-358.0094783779429</v>
+        <v>-368.5924183348876</v>
       </c>
       <c r="D73">
-        <v>220.5055216220571</v>
+        <v>218.1775816651124</v>
       </c>
       <c r="E73">
-        <v>508.305</v>
+        <v>516.5600000000001</v>
       </c>
       <c r="F73">
-        <v>586.105</v>
+        <v>594.36</v>
       </c>
       <c r="G73">
         <v>7.59</v>
@@ -7395,37 +7395,37 @@
         <v>19.56</v>
       </c>
       <c r="M73">
-        <v>138.203559</v>
+        <v>140.150088</v>
       </c>
       <c r="N73">
-        <v>-118.643559</v>
+        <v>-120.590088</v>
       </c>
       <c r="O73">
-        <v>-23.7287118</v>
+        <v>-24.1180176</v>
       </c>
       <c r="P73">
-        <v>-94.91484720000001</v>
+        <v>-96.47207040000001</v>
       </c>
       <c r="Q73">
-        <v>-86.47484720000001</v>
+        <v>-88.03207040000001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2110049466243749</v>
+        <v>0.2169051232895312</v>
       </c>
       <c r="T73">
-        <v>3.220151905514514</v>
+        <v>3.335157330711462</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.02830607278355255</v>
+        <v>0.02791293288378098</v>
       </c>
       <c r="W73">
-        <v>0.2291254280376383</v>
+        <v>0.2292181304260045</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7433,7 +7433,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1415303639177627</v>
+        <v>0.139564664418905</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7441,22 +7441,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2257704884277919</v>
+        <v>0.2276704884277919</v>
       </c>
       <c r="C74">
-        <v>-368.5924183348876</v>
+        <v>-379.1267183397825</v>
       </c>
       <c r="D74">
-        <v>218.1775816651124</v>
+        <v>215.8982816602175</v>
       </c>
       <c r="E74">
-        <v>516.5600000000001</v>
+        <v>524.8150000000001</v>
       </c>
       <c r="F74">
-        <v>594.36</v>
+        <v>602.615</v>
       </c>
       <c r="G74">
         <v>7.59</v>
@@ -7477,37 +7477,37 @@
         <v>19.56</v>
       </c>
       <c r="M74">
-        <v>140.150088</v>
+        <v>142.096617</v>
       </c>
       <c r="N74">
-        <v>-120.590088</v>
+        <v>-122.536617</v>
       </c>
       <c r="O74">
-        <v>-24.1180176</v>
+        <v>-24.5073234</v>
       </c>
       <c r="P74">
-        <v>-96.47207040000001</v>
+        <v>-98.0292936</v>
       </c>
       <c r="Q74">
-        <v>-88.03207040000001</v>
+        <v>-89.5892936</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2169051232895312</v>
+        <v>0.2232423500780323</v>
       </c>
       <c r="T74">
-        <v>3.335157330711462</v>
+        <v>3.458681676293367</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.02791293288378098</v>
+        <v>0.02753056394016755</v>
       </c>
       <c r="W74">
-        <v>0.2292181304260045</v>
+        <v>0.2293082930229085</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.139564664418905</v>
+        <v>0.1376528197008378</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7523,22 +7523,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2276704884277919</v>
+        <v>0.2295704884277919</v>
       </c>
       <c r="C75">
-        <v>-379.1267183397825</v>
+        <v>-389.613887055575</v>
       </c>
       <c r="D75">
-        <v>215.8982816602175</v>
+        <v>213.666112944425</v>
       </c>
       <c r="E75">
-        <v>524.8150000000001</v>
+        <v>533.0700000000001</v>
       </c>
       <c r="F75">
-        <v>602.615</v>
+        <v>610.87</v>
       </c>
       <c r="G75">
         <v>7.59</v>
@@ -7559,37 +7559,37 @@
         <v>19.56</v>
       </c>
       <c r="M75">
-        <v>142.096617</v>
+        <v>144.043146</v>
       </c>
       <c r="N75">
-        <v>-122.536617</v>
+        <v>-124.483146</v>
       </c>
       <c r="O75">
-        <v>-24.5073234</v>
+        <v>-24.8966292</v>
       </c>
       <c r="P75">
-        <v>-98.0292936</v>
+        <v>-99.5865168</v>
       </c>
       <c r="Q75">
-        <v>-89.5892936</v>
+        <v>-91.1465168</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2232423500780323</v>
+        <v>0.2300670558502643</v>
       </c>
       <c r="T75">
-        <v>3.458681676293367</v>
+        <v>3.591707894612343</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.02753056394016755</v>
+        <v>0.02715852929232744</v>
       </c>
       <c r="W75">
-        <v>0.2293082930229085</v>
+        <v>0.2293960187928692</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1376528197008378</v>
+        <v>0.1357926464616372</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7605,22 +7605,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2295704884277919</v>
+        <v>0.2314704884277919</v>
       </c>
       <c r="C76">
-        <v>-389.613887055575</v>
+        <v>-400.0553713915189</v>
       </c>
       <c r="D76">
-        <v>213.666112944425</v>
+        <v>211.4796286084812</v>
       </c>
       <c r="E76">
-        <v>533.0700000000001</v>
+        <v>541.325</v>
       </c>
       <c r="F76">
-        <v>610.87</v>
+        <v>619.125</v>
       </c>
       <c r="G76">
         <v>7.59</v>
@@ -7641,37 +7641,37 @@
         <v>19.56</v>
       </c>
       <c r="M76">
-        <v>144.043146</v>
+        <v>145.989675</v>
       </c>
       <c r="N76">
-        <v>-124.483146</v>
+        <v>-126.429675</v>
       </c>
       <c r="O76">
-        <v>-24.8966292</v>
+        <v>-25.285935</v>
       </c>
       <c r="P76">
-        <v>-99.5865168</v>
+        <v>-101.14374</v>
       </c>
       <c r="Q76">
-        <v>-91.1465168</v>
+        <v>-92.70374000000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2300670558502643</v>
+        <v>0.2374377380842749</v>
       </c>
       <c r="T76">
-        <v>3.591707894612343</v>
+        <v>3.735376210396837</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.02715852929232744</v>
+        <v>0.02679641556842974</v>
       </c>
       <c r="W76">
-        <v>0.2293960187928692</v>
+        <v>0.2294814052089643</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1357926464616372</v>
+        <v>0.1339820778421488</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7687,22 +7687,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2314704884277919</v>
+        <v>0.2333704884277919</v>
       </c>
       <c r="C77">
-        <v>-400.0553713915189</v>
+        <v>-410.4525596308526</v>
       </c>
       <c r="D77">
-        <v>211.4796286084812</v>
+        <v>209.3374403691474</v>
       </c>
       <c r="E77">
-        <v>541.325</v>
+        <v>549.58</v>
       </c>
       <c r="F77">
-        <v>619.125</v>
+        <v>627.38</v>
       </c>
       <c r="G77">
         <v>7.59</v>
@@ -7723,37 +7723,37 @@
         <v>19.56</v>
       </c>
       <c r="M77">
-        <v>145.989675</v>
+        <v>147.936204</v>
       </c>
       <c r="N77">
-        <v>-126.429675</v>
+        <v>-128.376204</v>
       </c>
       <c r="O77">
-        <v>-25.285935</v>
+        <v>-25.6752408</v>
       </c>
       <c r="P77">
-        <v>-101.14374</v>
+        <v>-102.7009632</v>
       </c>
       <c r="Q77">
-        <v>-92.70374000000001</v>
+        <v>-94.26096320000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2374377380842749</v>
+        <v>0.2454226438377863</v>
       </c>
       <c r="T77">
-        <v>3.735376210396837</v>
+        <v>3.891016885830038</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.02679641556842974</v>
+        <v>0.02644383115305567</v>
       </c>
       <c r="W77">
-        <v>0.2294814052089643</v>
+        <v>0.2295645446141095</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1339820778421488</v>
+        <v>0.1322191557652784</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7769,22 +7769,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2333704884277919</v>
+        <v>0.2352704884277919</v>
       </c>
       <c r="C78">
-        <v>-410.4525596308526</v>
+        <v>-420.8067843702925</v>
       </c>
       <c r="D78">
-        <v>209.3374403691474</v>
+        <v>207.2382156297076</v>
       </c>
       <c r="E78">
-        <v>549.58</v>
+        <v>557.835</v>
       </c>
       <c r="F78">
-        <v>627.38</v>
+        <v>635.635</v>
       </c>
       <c r="G78">
         <v>7.59</v>
@@ -7805,37 +7805,37 @@
         <v>19.56</v>
       </c>
       <c r="M78">
-        <v>147.936204</v>
+        <v>149.882733</v>
       </c>
       <c r="N78">
-        <v>-128.376204</v>
+        <v>-130.322733</v>
       </c>
       <c r="O78">
-        <v>-25.6752408</v>
+        <v>-26.0645466</v>
       </c>
       <c r="P78">
-        <v>-102.7009632</v>
+        <v>-104.2581864</v>
       </c>
       <c r="Q78">
-        <v>-94.26096320000001</v>
+        <v>-95.8181864</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2454226438377863</v>
+        <v>0.2541018892220379</v>
       </c>
       <c r="T78">
-        <v>3.891016885830038</v>
+        <v>4.060191533040041</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.02644383115305567</v>
+        <v>0.02610040477444456</v>
       </c>
       <c r="W78">
-        <v>0.2295645446141095</v>
+        <v>0.229645524554186</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.1322191557652784</v>
+        <v>0.1305020238722229</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7851,22 +7851,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2352704884277919</v>
+        <v>0.2371704884277919</v>
       </c>
       <c r="C79">
-        <v>-420.8067843702925</v>
+        <v>-431.1193252844184</v>
       </c>
       <c r="D79">
-        <v>207.2382156297076</v>
+        <v>205.1806747155815</v>
       </c>
       <c r="E79">
-        <v>557.835</v>
+        <v>566.09</v>
       </c>
       <c r="F79">
-        <v>635.635</v>
+        <v>643.89</v>
       </c>
       <c r="G79">
         <v>7.59</v>
@@ -7887,37 +7887,37 @@
         <v>19.56</v>
       </c>
       <c r="M79">
-        <v>149.882733</v>
+        <v>151.829262</v>
       </c>
       <c r="N79">
-        <v>-130.322733</v>
+        <v>-132.269262</v>
       </c>
       <c r="O79">
-        <v>-26.0645466</v>
+        <v>-26.4538524</v>
       </c>
       <c r="P79">
-        <v>-104.2581864</v>
+        <v>-105.8154096</v>
       </c>
       <c r="Q79">
-        <v>-95.8181864</v>
+        <v>-97.3754096</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2541018892220379</v>
+        <v>0.2635701569139487</v>
       </c>
       <c r="T79">
-        <v>4.060191533040041</v>
+        <v>4.24474569363277</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.02610040477444456</v>
+        <v>0.02576578420041322</v>
       </c>
       <c r="W79">
-        <v>0.229645524554186</v>
+        <v>0.2297244280855426</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1305020238722229</v>
+        <v>0.1288289210020661</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7933,22 +7933,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2371704884277919</v>
+        <v>0.2390704884277919</v>
       </c>
       <c r="C80">
-        <v>-431.1193252844184</v>
+        <v>-441.3914117270041</v>
       </c>
       <c r="D80">
-        <v>205.1806747155815</v>
+        <v>203.1635882729959</v>
       </c>
       <c r="E80">
-        <v>566.09</v>
+        <v>574.345</v>
       </c>
       <c r="F80">
-        <v>643.89</v>
+        <v>652.145</v>
       </c>
       <c r="G80">
         <v>7.59</v>
@@ -7969,37 +7969,37 @@
         <v>19.56</v>
       </c>
       <c r="M80">
-        <v>151.829262</v>
+        <v>153.775791</v>
       </c>
       <c r="N80">
-        <v>-132.269262</v>
+        <v>-134.215791</v>
       </c>
       <c r="O80">
-        <v>-26.4538524</v>
+        <v>-26.8431582</v>
       </c>
       <c r="P80">
-        <v>-105.8154096</v>
+        <v>-107.3726328</v>
       </c>
       <c r="Q80">
-        <v>-97.3754096</v>
+        <v>-98.93263279999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2635701569139487</v>
+        <v>0.2739401643860416</v>
       </c>
       <c r="T80">
-        <v>4.24474569363277</v>
+        <v>4.446876440948617</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.02576578420041322</v>
+        <v>0.02543963503331938</v>
       </c>
       <c r="W80">
-        <v>0.2297244280855426</v>
+        <v>0.2298013340591433</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8007,7 +8007,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1288289210020661</v>
+        <v>0.1271981751665969</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8015,22 +8015,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2390704884277919</v>
+        <v>0.2409704884277919</v>
       </c>
       <c r="C81">
-        <v>-441.3914117270041</v>
+        <v>-451.6242251804019</v>
       </c>
       <c r="D81">
-        <v>203.1635882729959</v>
+        <v>201.1857748195982</v>
       </c>
       <c r="E81">
-        <v>574.345</v>
+        <v>582.6000000000001</v>
       </c>
       <c r="F81">
-        <v>652.145</v>
+        <v>660.4000000000001</v>
       </c>
       <c r="G81">
         <v>7.59</v>
@@ -8051,37 +8051,37 @@
         <v>19.56</v>
       </c>
       <c r="M81">
-        <v>153.775791</v>
+        <v>155.72232</v>
       </c>
       <c r="N81">
-        <v>-134.215791</v>
+        <v>-136.16232</v>
       </c>
       <c r="O81">
-        <v>-26.8431582</v>
+        <v>-27.23246400000001</v>
       </c>
       <c r="P81">
-        <v>-107.3726328</v>
+        <v>-108.929856</v>
       </c>
       <c r="Q81">
-        <v>-98.93263279999999</v>
+        <v>-100.489856</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2739401643860416</v>
+        <v>0.2853471726053436</v>
       </c>
       <c r="T81">
-        <v>4.446876440948617</v>
+        <v>4.669220262996046</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.02543963503331938</v>
+        <v>0.02512163959540288</v>
       </c>
       <c r="W81">
-        <v>0.2298013340591433</v>
+        <v>0.229876317383404</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1271981751665969</v>
+        <v>0.1256081979770145</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8097,22 +8097,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2409704884277919</v>
+        <v>0.2428704884277919</v>
       </c>
       <c r="C82">
-        <v>-451.6242251804019</v>
+        <v>-461.8189015632373</v>
       </c>
       <c r="D82">
-        <v>201.1857748195982</v>
+        <v>199.2460984367627</v>
       </c>
       <c r="E82">
-        <v>582.6000000000001</v>
+        <v>590.8550000000001</v>
       </c>
       <c r="F82">
-        <v>660.4000000000001</v>
+        <v>668.6550000000001</v>
       </c>
       <c r="G82">
         <v>7.59</v>
@@ -8133,37 +8133,37 @@
         <v>19.56</v>
       </c>
       <c r="M82">
-        <v>155.72232</v>
+        <v>157.668849</v>
       </c>
       <c r="N82">
-        <v>-136.16232</v>
+        <v>-138.108849</v>
       </c>
       <c r="O82">
-        <v>-27.23246400000001</v>
+        <v>-27.62176980000001</v>
       </c>
       <c r="P82">
-        <v>-108.929856</v>
+        <v>-110.4870792</v>
       </c>
       <c r="Q82">
-        <v>-100.489856</v>
+        <v>-102.0470792</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2853471726053436</v>
+        <v>0.2979549185319407</v>
       </c>
       <c r="T82">
-        <v>4.669220262996046</v>
+        <v>4.914968697890576</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.02512163959540288</v>
+        <v>0.02481149589669421</v>
       </c>
       <c r="W82">
-        <v>0.229876317383404</v>
+        <v>0.2299494492675595</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.1256081979770145</v>
+        <v>0.1240574794834711</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8179,22 +8179,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2428704884277919</v>
+        <v>0.2447704884277919</v>
       </c>
       <c r="C83">
-        <v>-461.8189015632373</v>
+        <v>-471.9765334058849</v>
       </c>
       <c r="D83">
-        <v>199.2460984367627</v>
+        <v>197.3434665941152</v>
       </c>
       <c r="E83">
-        <v>590.8550000000001</v>
+        <v>599.1100000000001</v>
       </c>
       <c r="F83">
-        <v>668.6550000000001</v>
+        <v>676.9100000000001</v>
       </c>
       <c r="G83">
         <v>7.59</v>
@@ -8215,37 +8215,37 @@
         <v>19.56</v>
       </c>
       <c r="M83">
-        <v>157.668849</v>
+        <v>159.615378</v>
       </c>
       <c r="N83">
-        <v>-138.108849</v>
+        <v>-140.055378</v>
       </c>
       <c r="O83">
-        <v>-27.62176980000001</v>
+        <v>-28.01107560000001</v>
       </c>
       <c r="P83">
-        <v>-110.4870792</v>
+        <v>-112.0443024</v>
       </c>
       <c r="Q83">
-        <v>-102.0470792</v>
+        <v>-103.6043024</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2979549185319407</v>
+        <v>0.3119635251170486</v>
       </c>
       <c r="T83">
-        <v>4.914968697890576</v>
+        <v>5.188022514440053</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.02481149589669421</v>
+        <v>0.02450891667844184</v>
       </c>
       <c r="W83">
-        <v>0.2299494492675595</v>
+        <v>0.2300207974472234</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1240574794834711</v>
+        <v>0.1225445833922092</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8261,22 +8261,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2447704884277919</v>
+        <v>0.2466704884277919</v>
       </c>
       <c r="C84">
-        <v>-471.9765334058849</v>
+        <v>-482.0981719024782</v>
       </c>
       <c r="D84">
-        <v>197.3434665941152</v>
+        <v>195.4768280975219</v>
       </c>
       <c r="E84">
-        <v>599.1100000000001</v>
+        <v>607.3650000000001</v>
       </c>
       <c r="F84">
-        <v>676.9100000000001</v>
+        <v>685.1650000000001</v>
       </c>
       <c r="G84">
         <v>7.59</v>
@@ -8297,37 +8297,37 @@
         <v>19.56</v>
       </c>
       <c r="M84">
-        <v>159.615378</v>
+        <v>161.561907</v>
       </c>
       <c r="N84">
-        <v>-140.055378</v>
+        <v>-142.001907</v>
       </c>
       <c r="O84">
-        <v>-28.01107560000001</v>
+        <v>-28.4003814</v>
       </c>
       <c r="P84">
-        <v>-112.0443024</v>
+        <v>-113.6015256</v>
       </c>
       <c r="Q84">
-        <v>-103.6043024</v>
+        <v>-105.1615256</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3119635251170486</v>
+        <v>0.3276202030651102</v>
       </c>
       <c r="T84">
-        <v>5.188022514440053</v>
+        <v>5.493200309407115</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.02450891667844184</v>
+        <v>0.02421362852568953</v>
       </c>
       <c r="W84">
-        <v>0.2300207974472234</v>
+        <v>0.2300904263936424</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.1225445833922092</v>
+        <v>0.1210681426284477</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8343,22 +8343,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2466704884277919</v>
+        <v>0.2485704884277919</v>
       </c>
       <c r="C85">
-        <v>-482.0981719024782</v>
+        <v>-492.1848288475546</v>
       </c>
       <c r="D85">
-        <v>195.4768280975219</v>
+        <v>193.6451711524455</v>
       </c>
       <c r="E85">
-        <v>607.3650000000001</v>
+        <v>615.6200000000001</v>
       </c>
       <c r="F85">
-        <v>685.1650000000001</v>
+        <v>693.4200000000001</v>
       </c>
       <c r="G85">
         <v>7.59</v>
@@ -8379,37 +8379,37 @@
         <v>19.56</v>
       </c>
       <c r="M85">
-        <v>161.561907</v>
+        <v>163.508436</v>
       </c>
       <c r="N85">
-        <v>-142.001907</v>
+        <v>-143.948436</v>
       </c>
       <c r="O85">
-        <v>-28.4003814</v>
+        <v>-28.7896872</v>
       </c>
       <c r="P85">
-        <v>-113.6015256</v>
+        <v>-115.1587488</v>
       </c>
       <c r="Q85">
-        <v>-105.1615256</v>
+        <v>-106.7187488</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3276202030651102</v>
+        <v>0.3452339657566796</v>
       </c>
       <c r="T85">
-        <v>5.493200309407115</v>
+        <v>5.836525328745061</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.02421362852568953</v>
+        <v>0.02392537104324084</v>
       </c>
       <c r="W85">
-        <v>0.2300904263936424</v>
+        <v>0.2301583975080038</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1210681426284477</v>
+        <v>0.1196268552162043</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8425,22 +8425,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2485704884277919</v>
+        <v>0.2504704884277919</v>
       </c>
       <c r="C86">
-        <v>-492.1848288475545</v>
+        <v>-502.2374784648291</v>
       </c>
       <c r="D86">
-        <v>193.6451711524455</v>
+        <v>191.8475215351708</v>
       </c>
       <c r="E86">
-        <v>615.62</v>
+        <v>623.875</v>
       </c>
       <c r="F86">
-        <v>693.42</v>
+        <v>701.675</v>
       </c>
       <c r="G86">
         <v>7.59</v>
@@ -8461,37 +8461,37 @@
         <v>19.56</v>
       </c>
       <c r="M86">
-        <v>163.508436</v>
+        <v>165.454965</v>
       </c>
       <c r="N86">
-        <v>-143.948436</v>
+        <v>-145.894965</v>
       </c>
       <c r="O86">
-        <v>-28.7896872</v>
+        <v>-29.178993</v>
       </c>
       <c r="P86">
-        <v>-115.1587488</v>
+        <v>-116.715972</v>
       </c>
       <c r="Q86">
-        <v>-106.7187488</v>
+        <v>-108.275972</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3452339657566794</v>
+        <v>0.3651962301404581</v>
       </c>
       <c r="T86">
-        <v>5.836525328745057</v>
+        <v>6.225627017328061</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.02392537104324085</v>
+        <v>0.02364389608979096</v>
       </c>
       <c r="W86">
-        <v>0.2301583975080038</v>
+        <v>0.2302247693020273</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.1196268552162043</v>
+        <v>0.1182194804489548</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8507,22 +8507,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2504704884277919</v>
+        <v>0.2523704884277919</v>
       </c>
       <c r="C87">
-        <v>-502.2374784648291</v>
+        <v>-512.2570591350454</v>
       </c>
       <c r="D87">
-        <v>191.8475215351708</v>
+        <v>190.0829408649545</v>
       </c>
       <c r="E87">
-        <v>623.875</v>
+        <v>632.13</v>
       </c>
       <c r="F87">
-        <v>701.675</v>
+        <v>709.9299999999999</v>
       </c>
       <c r="G87">
         <v>7.59</v>
@@ -8543,37 +8543,37 @@
         <v>19.56</v>
       </c>
       <c r="M87">
-        <v>165.454965</v>
+        <v>167.401494</v>
       </c>
       <c r="N87">
-        <v>-145.894965</v>
+        <v>-147.841494</v>
       </c>
       <c r="O87">
-        <v>-29.178993</v>
+        <v>-29.5682988</v>
       </c>
       <c r="P87">
-        <v>-116.715972</v>
+        <v>-118.2731952</v>
       </c>
       <c r="Q87">
-        <v>-108.275972</v>
+        <v>-109.8331952</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3651962301404581</v>
+        <v>0.3880102465790622</v>
       </c>
       <c r="T87">
-        <v>6.225627017328061</v>
+        <v>6.670314661422923</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.02364389608979096</v>
+        <v>0.02336896706549106</v>
       </c>
       <c r="W87">
-        <v>0.2302247693020273</v>
+        <v>0.2302895975659572</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8581,7 +8581,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1182194804489548</v>
+        <v>0.1168448353274554</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8589,22 +8589,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2523704884277919</v>
+        <v>0.2542704884277919</v>
       </c>
       <c r="C88">
-        <v>-512.2570591350454</v>
+        <v>-522.2444750293388</v>
       </c>
       <c r="D88">
-        <v>190.0829408649545</v>
+        <v>188.3505249706611</v>
       </c>
       <c r="E88">
-        <v>632.13</v>
+        <v>640.385</v>
       </c>
       <c r="F88">
-        <v>709.9299999999999</v>
+        <v>718.1849999999999</v>
       </c>
       <c r="G88">
         <v>7.59</v>
@@ -8625,37 +8625,37 @@
         <v>19.56</v>
       </c>
       <c r="M88">
-        <v>167.401494</v>
+        <v>169.348023</v>
       </c>
       <c r="N88">
-        <v>-147.841494</v>
+        <v>-149.788023</v>
       </c>
       <c r="O88">
-        <v>-29.5682988</v>
+        <v>-29.9576046</v>
       </c>
       <c r="P88">
-        <v>-118.2731952</v>
+        <v>-119.8304184</v>
       </c>
       <c r="Q88">
-        <v>-109.8331952</v>
+        <v>-111.3904184</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3880102465790622</v>
+        <v>0.4143341117005286</v>
       </c>
       <c r="T88">
-        <v>6.670314661422923</v>
+        <v>7.183415789224687</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.02336896706549106</v>
+        <v>0.02310035824864634</v>
       </c>
       <c r="W88">
-        <v>0.2302895975659572</v>
+        <v>0.2303529355249692</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1168448353274554</v>
+        <v>0.1155017912432317</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8671,22 +8671,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2542704884277919</v>
+        <v>0.2561704884277919</v>
       </c>
       <c r="C89">
-        <v>-522.2444750293388</v>
+        <v>-532.2005976540892</v>
       </c>
       <c r="D89">
-        <v>188.3505249706611</v>
+        <v>186.6494023459109</v>
       </c>
       <c r="E89">
-        <v>640.385</v>
+        <v>648.6400000000001</v>
       </c>
       <c r="F89">
-        <v>718.1849999999999</v>
+        <v>726.4400000000001</v>
       </c>
       <c r="G89">
         <v>7.59</v>
@@ -8707,37 +8707,37 @@
         <v>19.56</v>
       </c>
       <c r="M89">
-        <v>169.348023</v>
+        <v>171.294552</v>
       </c>
       <c r="N89">
-        <v>-149.788023</v>
+        <v>-151.734552</v>
       </c>
       <c r="O89">
-        <v>-29.9576046</v>
+        <v>-30.3469104</v>
       </c>
       <c r="P89">
-        <v>-119.8304184</v>
+        <v>-121.3876416</v>
       </c>
       <c r="Q89">
-        <v>-111.3904184</v>
+        <v>-112.9476416</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4143341117005286</v>
+        <v>0.4450452876755727</v>
       </c>
       <c r="T89">
-        <v>7.183415789224687</v>
+        <v>7.782033771660078</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02310035824864634</v>
+        <v>0.02283785417763899</v>
       </c>
       <c r="W89">
-        <v>0.2303529355249692</v>
+        <v>0.2304148339849127</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1155017912432317</v>
+        <v>0.114189270888195</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8753,22 +8753,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2561704884277919</v>
+        <v>0.2580704884277919</v>
       </c>
       <c r="C90">
-        <v>-532.2005976540892</v>
+        <v>-542.1262673128056</v>
       </c>
       <c r="D90">
-        <v>186.6494023459109</v>
+        <v>184.9787326871945</v>
       </c>
       <c r="E90">
-        <v>648.6400000000001</v>
+        <v>656.8950000000001</v>
       </c>
       <c r="F90">
-        <v>726.4400000000001</v>
+        <v>734.6950000000001</v>
       </c>
       <c r="G90">
         <v>7.59</v>
@@ -8789,37 +8789,37 @@
         <v>19.56</v>
       </c>
       <c r="M90">
-        <v>171.294552</v>
+        <v>173.241081</v>
       </c>
       <c r="N90">
-        <v>-151.734552</v>
+        <v>-153.681081</v>
       </c>
       <c r="O90">
-        <v>-30.3469104</v>
+        <v>-30.7362162</v>
       </c>
       <c r="P90">
-        <v>-121.3876416</v>
+        <v>-122.9448648</v>
       </c>
       <c r="Q90">
-        <v>-112.9476416</v>
+        <v>-114.5048648</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4450452876755727</v>
+        <v>0.4813403138278975</v>
       </c>
       <c r="T90">
-        <v>7.782033771660078</v>
+        <v>8.48949138726554</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02283785417763899</v>
+        <v>0.02258124907451945</v>
       </c>
       <c r="W90">
-        <v>0.2304148339849127</v>
+        <v>0.2304753414682283</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.114189270888195</v>
+        <v>0.1129062453725973</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8835,22 +8835,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2580704884277919</v>
+        <v>0.2599704884277919</v>
       </c>
       <c r="C91">
-        <v>-542.1262673128056</v>
+        <v>-552.0222944901991</v>
       </c>
       <c r="D91">
-        <v>184.9787326871945</v>
+        <v>183.3377055098009</v>
       </c>
       <c r="E91">
-        <v>656.8950000000001</v>
+        <v>665.1500000000001</v>
       </c>
       <c r="F91">
-        <v>734.6950000000001</v>
+        <v>742.95</v>
       </c>
       <c r="G91">
         <v>7.59</v>
@@ -8871,37 +8871,37 @@
         <v>19.56</v>
       </c>
       <c r="M91">
-        <v>173.241081</v>
+        <v>175.18761</v>
       </c>
       <c r="N91">
-        <v>-153.681081</v>
+        <v>-155.62761</v>
       </c>
       <c r="O91">
-        <v>-30.7362162</v>
+        <v>-31.125522</v>
       </c>
       <c r="P91">
-        <v>-122.9448648</v>
+        <v>-124.502088</v>
       </c>
       <c r="Q91">
-        <v>-114.5048648</v>
+        <v>-116.062088</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4813403138278975</v>
+        <v>0.5248943452106872</v>
       </c>
       <c r="T91">
-        <v>8.48949138726554</v>
+        <v>9.338440525992095</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02258124907451945</v>
+        <v>0.02233034630702479</v>
       </c>
       <c r="W91">
-        <v>0.2304753414682283</v>
+        <v>0.2305345043408036</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1129062453725973</v>
+        <v>0.111651731535124</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8917,22 +8917,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2599704884277919</v>
+        <v>0.2618704884277919</v>
       </c>
       <c r="C92">
-        <v>-552.0222944901991</v>
+        <v>-561.8894611632292</v>
       </c>
       <c r="D92">
-        <v>183.3377055098009</v>
+        <v>181.7255388367709</v>
       </c>
       <c r="E92">
-        <v>665.1500000000001</v>
+        <v>673.4050000000001</v>
       </c>
       <c r="F92">
-        <v>742.95</v>
+        <v>751.205</v>
       </c>
       <c r="G92">
         <v>7.59</v>
@@ -8953,37 +8953,37 @@
         <v>19.56</v>
       </c>
       <c r="M92">
-        <v>175.18761</v>
+        <v>177.134139</v>
       </c>
       <c r="N92">
-        <v>-155.62761</v>
+        <v>-157.574139</v>
       </c>
       <c r="O92">
-        <v>-31.125522</v>
+        <v>-31.5148278</v>
       </c>
       <c r="P92">
-        <v>-124.502088</v>
+        <v>-126.0593112</v>
       </c>
       <c r="Q92">
-        <v>-116.062088</v>
+        <v>-117.6193112</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5248943452106872</v>
+        <v>0.5781270502340971</v>
       </c>
       <c r="T92">
-        <v>9.338440525992095</v>
+        <v>10.37604502888011</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02233034630702479</v>
+        <v>0.02208495788606847</v>
       </c>
       <c r="W92">
-        <v>0.2305345043408036</v>
+        <v>0.2305923669304651</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.111651731535124</v>
+        <v>0.1104247894303424</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8999,22 +8999,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2618704884277919</v>
+        <v>0.2637704884277919</v>
       </c>
       <c r="C93">
-        <v>-561.8894611632292</v>
+        <v>-571.7285220435821</v>
       </c>
       <c r="D93">
-        <v>181.7255388367709</v>
+        <v>180.141477956418</v>
       </c>
       <c r="E93">
-        <v>673.4050000000001</v>
+        <v>681.6600000000001</v>
       </c>
       <c r="F93">
-        <v>751.205</v>
+        <v>759.46</v>
       </c>
       <c r="G93">
         <v>7.59</v>
@@ -9035,37 +9035,37 @@
         <v>19.56</v>
       </c>
       <c r="M93">
-        <v>177.134139</v>
+        <v>179.080668</v>
       </c>
       <c r="N93">
-        <v>-157.574139</v>
+        <v>-159.520668</v>
       </c>
       <c r="O93">
-        <v>-31.5148278</v>
+        <v>-31.9041336</v>
       </c>
       <c r="P93">
-        <v>-126.0593112</v>
+        <v>-127.6165344</v>
       </c>
       <c r="Q93">
-        <v>-117.6193112</v>
+        <v>-119.1765344</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5781270502340971</v>
+        <v>0.6446679315133593</v>
       </c>
       <c r="T93">
-        <v>10.37604502888011</v>
+        <v>11.67305065749012</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02208495788606847</v>
+        <v>0.02184490399600251</v>
       </c>
       <c r="W93">
-        <v>0.2305923669304651</v>
+        <v>0.2306489716377426</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9073,7 +9073,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1104247894303424</v>
+        <v>0.1092245199800126</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9081,22 +9081,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2637704884277919</v>
+        <v>0.265670488427792</v>
       </c>
       <c r="C94">
-        <v>-571.7285220435821</v>
+        <v>-581.5402057557283</v>
       </c>
       <c r="D94">
-        <v>180.141477956418</v>
+        <v>178.5847942442717</v>
       </c>
       <c r="E94">
-        <v>681.6600000000001</v>
+        <v>689.9150000000001</v>
       </c>
       <c r="F94">
-        <v>759.46</v>
+        <v>767.715</v>
       </c>
       <c r="G94">
         <v>7.59</v>
@@ -9117,37 +9117,37 @@
         <v>19.56</v>
       </c>
       <c r="M94">
-        <v>179.080668</v>
+        <v>181.027197</v>
       </c>
       <c r="N94">
-        <v>-159.520668</v>
+        <v>-161.467197</v>
       </c>
       <c r="O94">
-        <v>-31.9041336</v>
+        <v>-32.2934394</v>
       </c>
       <c r="P94">
-        <v>-127.6165344</v>
+        <v>-129.1737576</v>
       </c>
       <c r="Q94">
-        <v>-119.1765344</v>
+        <v>-120.7337576</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6446679315133593</v>
+        <v>0.730220493158125</v>
       </c>
       <c r="T94">
-        <v>11.67305065749012</v>
+        <v>13.34062932284586</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02184490399600251</v>
+        <v>0.02161001255518528</v>
       </c>
       <c r="W94">
-        <v>0.2306489716377426</v>
+        <v>0.2307043590394873</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9155,7 +9155,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1092245199800126</v>
+        <v>0.1080500627759264</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9163,22 +9163,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.265670488427792</v>
+        <v>0.2675704884277919</v>
       </c>
       <c r="C95">
-        <v>-581.5402057557283</v>
+        <v>-591.3252159544234</v>
       </c>
       <c r="D95">
-        <v>178.5847942442717</v>
+        <v>177.0547840455766</v>
       </c>
       <c r="E95">
-        <v>689.9150000000001</v>
+        <v>698.1700000000001</v>
       </c>
       <c r="F95">
-        <v>767.715</v>
+        <v>775.97</v>
       </c>
       <c r="G95">
         <v>7.59</v>
@@ -9199,37 +9199,37 @@
         <v>19.56</v>
       </c>
       <c r="M95">
-        <v>181.027197</v>
+        <v>182.973726</v>
       </c>
       <c r="N95">
-        <v>-161.467197</v>
+        <v>-163.413726</v>
       </c>
       <c r="O95">
-        <v>-32.2934394</v>
+        <v>-32.68274520000001</v>
       </c>
       <c r="P95">
-        <v>-129.1737576</v>
+        <v>-130.7309808</v>
       </c>
       <c r="Q95">
-        <v>-120.7337576</v>
+        <v>-122.2909808</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.730220493158125</v>
+        <v>0.8442905753511459</v>
       </c>
       <c r="T95">
-        <v>13.34062932284586</v>
+        <v>15.56406754332017</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02161001255518528</v>
+        <v>0.0213801188045982</v>
       </c>
       <c r="W95">
-        <v>0.2307043590394873</v>
+        <v>0.2307585679858757</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9237,7 +9237,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1080500627759264</v>
+        <v>0.106900594022991</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9245,22 +9245,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2675704884277919</v>
+        <v>0.2694704884277919</v>
       </c>
       <c r="C96">
-        <v>-591.3252159544234</v>
+        <v>-601.0842323852509</v>
       </c>
       <c r="D96">
-        <v>177.0547840455766</v>
+        <v>175.5507676147492</v>
       </c>
       <c r="E96">
-        <v>698.1700000000001</v>
+        <v>706.4250000000001</v>
       </c>
       <c r="F96">
-        <v>775.97</v>
+        <v>784.225</v>
       </c>
       <c r="G96">
         <v>7.59</v>
@@ -9281,37 +9281,37 @@
         <v>19.56</v>
       </c>
       <c r="M96">
-        <v>182.973726</v>
+        <v>184.920255</v>
       </c>
       <c r="N96">
-        <v>-163.413726</v>
+        <v>-165.360255</v>
       </c>
       <c r="O96">
-        <v>-32.68274520000001</v>
+        <v>-33.07205100000001</v>
       </c>
       <c r="P96">
-        <v>-130.7309808</v>
+        <v>-132.288204</v>
       </c>
       <c r="Q96">
-        <v>-122.2909808</v>
+        <v>-123.848204</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8442905753511459</v>
+        <v>1.003988690421376</v>
       </c>
       <c r="T96">
-        <v>15.56406754332017</v>
+        <v>18.67688105198421</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.0213801188045982</v>
+        <v>0.02115506492244454</v>
       </c>
       <c r="W96">
-        <v>0.2307585679858757</v>
+        <v>0.2308116356912876</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.106900594022991</v>
+        <v>0.1057753246122227</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9327,22 +9327,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2694704884277919</v>
+        <v>0.2713704884277919</v>
       </c>
       <c r="C97">
-        <v>-601.0842323852509</v>
+        <v>-610.8179118915675</v>
       </c>
       <c r="D97">
-        <v>175.5507676147492</v>
+        <v>174.0720881084325</v>
       </c>
       <c r="E97">
-        <v>706.4250000000001</v>
+        <v>714.6800000000001</v>
       </c>
       <c r="F97">
-        <v>784.225</v>
+        <v>792.48</v>
       </c>
       <c r="G97">
         <v>7.59</v>
@@ -9363,37 +9363,37 @@
         <v>19.56</v>
       </c>
       <c r="M97">
-        <v>184.920255</v>
+        <v>186.866784</v>
       </c>
       <c r="N97">
-        <v>-165.360255</v>
+        <v>-167.306784</v>
       </c>
       <c r="O97">
-        <v>-33.07205100000001</v>
+        <v>-33.4613568</v>
       </c>
       <c r="P97">
-        <v>-132.288204</v>
+        <v>-133.8454272</v>
       </c>
       <c r="Q97">
-        <v>-123.848204</v>
+        <v>-125.4054272</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.003988690421376</v>
+        <v>1.24353586302672</v>
       </c>
       <c r="T97">
-        <v>18.67688105198421</v>
+        <v>23.34610131498027</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02115506492244454</v>
+        <v>0.02093469966283574</v>
       </c>
       <c r="W97">
-        <v>0.2308116356912876</v>
+        <v>0.2308635978195033</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9401,7 +9401,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1057753246122227</v>
+        <v>0.1046734983141787</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9409,22 +9409,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2713704884277919</v>
+        <v>0.2732704884277919</v>
       </c>
       <c r="C98">
-        <v>-610.8179118915675</v>
+        <v>-620.5268893709847</v>
       </c>
       <c r="D98">
-        <v>174.0720881084325</v>
+        <v>172.6181106290154</v>
       </c>
       <c r="E98">
-        <v>714.6800000000001</v>
+        <v>722.9350000000001</v>
       </c>
       <c r="F98">
-        <v>792.48</v>
+        <v>800.735</v>
       </c>
       <c r="G98">
         <v>7.59</v>
@@ -9445,37 +9445,37 @@
         <v>19.56</v>
       </c>
       <c r="M98">
-        <v>186.866784</v>
+        <v>188.813313</v>
       </c>
       <c r="N98">
-        <v>-167.306784</v>
+        <v>-169.253313</v>
       </c>
       <c r="O98">
-        <v>-33.4613568</v>
+        <v>-33.85066260000001</v>
       </c>
       <c r="P98">
-        <v>-133.8454272</v>
+        <v>-135.4026504</v>
       </c>
       <c r="Q98">
-        <v>-125.4054272</v>
+        <v>-126.9626504</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.243535863026717</v>
+        <v>1.642781150702289</v>
       </c>
       <c r="T98">
-        <v>23.34610131498021</v>
+        <v>31.12813508664028</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02093469966283574</v>
+        <v>0.02071887801682712</v>
       </c>
       <c r="W98">
-        <v>0.2308635978195033</v>
+        <v>0.2309144885636322</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1046734983141787</v>
+        <v>0.1035943900841356</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9491,22 +9491,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2732704884277919</v>
+        <v>0.2751704884277919</v>
       </c>
       <c r="C99">
-        <v>-620.5268893709847</v>
+        <v>-630.21177868431</v>
       </c>
       <c r="D99">
-        <v>172.6181106290154</v>
+        <v>171.18822131569</v>
       </c>
       <c r="E99">
-        <v>722.9350000000001</v>
+        <v>731.1900000000001</v>
       </c>
       <c r="F99">
-        <v>800.735</v>
+        <v>808.99</v>
       </c>
       <c r="G99">
         <v>7.59</v>
@@ -9527,37 +9527,37 @@
         <v>19.56</v>
       </c>
       <c r="M99">
-        <v>188.813313</v>
+        <v>190.759842</v>
       </c>
       <c r="N99">
-        <v>-169.253313</v>
+        <v>-171.199842</v>
       </c>
       <c r="O99">
-        <v>-33.85066260000001</v>
+        <v>-34.2399684</v>
       </c>
       <c r="P99">
-        <v>-135.4026504</v>
+        <v>-136.9598736</v>
       </c>
       <c r="Q99">
-        <v>-126.9626504</v>
+        <v>-128.5198736</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.642781150702289</v>
+        <v>2.441271726053434</v>
       </c>
       <c r="T99">
-        <v>31.12813508664028</v>
+        <v>46.69220262996043</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02071887801682712</v>
+        <v>0.02050746089420644</v>
       </c>
       <c r="W99">
-        <v>0.2309144885636322</v>
+        <v>0.2309643407211461</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9565,7 +9565,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1035943900841356</v>
+        <v>0.1025373044710323</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9573,22 +9573,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2751704884277919</v>
+        <v>0.2770704884277919</v>
       </c>
       <c r="C100">
-        <v>-630.21177868431</v>
+        <v>-639.8731735196864</v>
       </c>
       <c r="D100">
-        <v>171.18822131569</v>
+        <v>169.7818264803136</v>
       </c>
       <c r="E100">
-        <v>731.1900000000001</v>
+        <v>739.4450000000001</v>
       </c>
       <c r="F100">
-        <v>808.99</v>
+        <v>817.245</v>
       </c>
       <c r="G100">
         <v>7.59</v>
@@ -9609,37 +9609,37 @@
         <v>19.56</v>
       </c>
       <c r="M100">
-        <v>190.759842</v>
+        <v>192.706371</v>
       </c>
       <c r="N100">
-        <v>-171.199842</v>
+        <v>-173.146371</v>
       </c>
       <c r="O100">
-        <v>-34.2399684</v>
+        <v>-34.6292742</v>
       </c>
       <c r="P100">
-        <v>-136.9598736</v>
+        <v>-138.5170968</v>
       </c>
       <c r="Q100">
-        <v>-128.5198736</v>
+        <v>-130.0770968</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.441271726053434</v>
+        <v>4.836743452106868</v>
       </c>
       <c r="T100">
-        <v>46.69220262996043</v>
+        <v>93.38440525992085</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02050746089420644</v>
+        <v>0.02030031482456799</v>
       </c>
       <c r="W100">
-        <v>0.2309643407211461</v>
+        <v>0.2310131857643669</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9647,91 +9647,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1025373044710323</v>
+        <v>0.10150157412284</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2770704884277919</v>
-      </c>
-      <c r="C101">
-        <v>-639.8731735196864</v>
-      </c>
-      <c r="D101">
-        <v>169.7818264803136</v>
-      </c>
-      <c r="E101">
-        <v>739.4450000000001</v>
-      </c>
-      <c r="F101">
-        <v>817.245</v>
-      </c>
-      <c r="G101">
-        <v>7.59</v>
-      </c>
-      <c r="H101">
-        <v>747.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>28</v>
-      </c>
-      <c r="K101">
-        <v>8.44</v>
-      </c>
-      <c r="L101">
-        <v>19.56</v>
-      </c>
-      <c r="M101">
-        <v>192.706371</v>
-      </c>
-      <c r="N101">
-        <v>-173.146371</v>
-      </c>
-      <c r="O101">
-        <v>-34.6292742</v>
-      </c>
-      <c r="P101">
-        <v>-138.5170968</v>
-      </c>
-      <c r="Q101">
-        <v>-130.0770968</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.836743452106868</v>
-      </c>
-      <c r="T101">
-        <v>93.38440525992085</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02030031482456799</v>
-      </c>
-      <c r="W101">
-        <v>0.2310131857643669</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.10150157412284</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
